--- a/outputs/SAFIYA_против_Кореи.xlsx
+++ b/outputs/SAFIYA_против_Кореи.xlsx
@@ -505,10 +505,10 @@
         <v>31.4</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>19.4</v>
       </c>
       <c r="F2" t="n">
-        <v>103</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -527,10 +527,10 @@
         <v>41.6</v>
       </c>
       <c r="E3" t="n">
-        <v>8.9</v>
+        <v>28.8</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         <v>1161</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1509</v>
+        <v>1277</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>11.18</v>
@@ -692,7 +692,7 @@
         <v>-12.4</v>
       </c>
       <c r="L2" t="n">
-        <v>-32.6</v>
+        <v>-20.4</v>
       </c>
     </row>
     <row r="3">
@@ -728,7 +728,7 @@
         <v>896</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1165</v>
+        <v>986</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>9.140000000000001</v>
@@ -740,7 +740,7 @@
         <v>-7.1</v>
       </c>
       <c r="L3" t="n">
-        <v>-28.6</v>
+        <v>-15.6</v>
       </c>
     </row>
     <row r="4">
@@ -776,7 +776,7 @@
         <v>832</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1082</v>
+        <v>915</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>8.9</v>
@@ -788,7 +788,7 @@
         <v>-2.6</v>
       </c>
       <c r="L4" t="n">
-        <v>-25.1</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="5">
@@ -824,7 +824,7 @@
         <v>1843</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2396</v>
+        <v>2027</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>19.76</v>
@@ -836,7 +836,7 @@
         <v>-2.4</v>
       </c>
       <c r="L5" t="n">
-        <v>-25</v>
+        <v>-11.3</v>
       </c>
     </row>
     <row r="6">
@@ -872,7 +872,7 @@
         <v>1918</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2493</v>
+        <v>2110</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>20.82</v>
@@ -884,7 +884,7 @@
         <v>-1.2</v>
       </c>
       <c r="L6" t="n">
-        <v>-24</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="7">
@@ -920,7 +920,7 @@
         <v>1032</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1342</v>
+        <v>1135</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.42</v>
@@ -932,7 +932,7 @@
         <v>0.7</v>
       </c>
       <c r="L7" t="n">
-        <v>-22.6</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
         <v>821</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1067</v>
+        <v>903</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>9.140000000000001</v>
@@ -980,7 +980,7 @@
         <v>1.3</v>
       </c>
       <c r="L8" t="n">
-        <v>-22</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="9">
@@ -1016,7 +1016,7 @@
         <v>1257</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1634</v>
+        <v>1383</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>14.14</v>
@@ -1028,7 +1028,7 @@
         <v>2.4</v>
       </c>
       <c r="L9" t="n">
-        <v>-21.2</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="10">
@@ -1064,7 +1064,7 @@
         <v>808</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1050</v>
+        <v>889</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>9.140000000000001</v>
@@ -1076,7 +1076,7 @@
         <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>-20.8</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="11">
@@ -1112,7 +1112,7 @@
         <v>1257</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1634</v>
+        <v>1383</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>14.3</v>
@@ -1124,7 +1124,7 @@
         <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>-20.4</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="12">
@@ -1160,7 +1160,7 @@
         <v>839</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1091</v>
+        <v>923</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>9.550000000000001</v>
@@ -1172,7 +1172,7 @@
         <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>-20.3</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="13">
@@ -1208,7 +1208,7 @@
         <v>837</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1088</v>
+        <v>921</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>9.550000000000001</v>
@@ -1220,7 +1220,7 @@
         <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>-20.1</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="14">
@@ -1256,7 +1256,7 @@
         <v>614</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>798</v>
+        <v>675</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>7.02</v>
@@ -1268,7 +1268,7 @@
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>-19.9</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="15">
@@ -1304,7 +1304,7 @@
         <v>614</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>798</v>
+        <v>675</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>7.02</v>
@@ -1316,7 +1316,7 @@
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>-19.9</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="16">
@@ -1352,7 +1352,7 @@
         <v>905</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1176</v>
+        <v>996</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>10.38</v>
@@ -1364,7 +1364,7 @@
         <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>-19.6</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="17">
@@ -1400,7 +1400,7 @@
         <v>965</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1254</v>
+        <v>1062</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>11.18</v>
@@ -1412,7 +1412,7 @@
         <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>-18.9</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="18">
@@ -1448,7 +1448,7 @@
         <v>712</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>926</v>
+        <v>783</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>8.27</v>
@@ -1460,7 +1460,7 @@
         <v>5.8</v>
       </c>
       <c r="L18" t="n">
-        <v>-18.7</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="19">
@@ -1496,7 +1496,7 @@
         <v>712</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>926</v>
+        <v>783</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>8.27</v>
@@ -1508,7 +1508,7 @@
         <v>5.8</v>
       </c>
       <c r="L19" t="n">
-        <v>-18.7</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="20">
@@ -1544,7 +1544,7 @@
         <v>614</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>798</v>
+        <v>675</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>7.19</v>
@@ -1556,7 +1556,7 @@
         <v>6.5</v>
       </c>
       <c r="L20" t="n">
-        <v>-18</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="21">
@@ -1592,7 +1592,7 @@
         <v>1128</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1466</v>
+        <v>1241</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>13.21</v>
@@ -1604,7 +1604,7 @@
         <v>6.6</v>
       </c>
       <c r="L21" t="n">
-        <v>-18</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="22">
@@ -1640,7 +1640,7 @@
         <v>614</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>798</v>
+        <v>675</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>7.21</v>
@@ -1652,7 +1652,7 @@
         <v>6.8</v>
       </c>
       <c r="L22" t="n">
-        <v>-17.8</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="23">
@@ -1688,7 +1688,7 @@
         <v>652</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>848</v>
+        <v>717</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>7.67</v>
@@ -1700,7 +1700,7 @@
         <v>7.1</v>
       </c>
       <c r="L23" t="n">
-        <v>-17.7</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="24">
@@ -1736,7 +1736,7 @@
         <v>750</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>975</v>
+        <v>825</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>8.83</v>
@@ -1748,7 +1748,7 @@
         <v>7.2</v>
       </c>
       <c r="L24" t="n">
-        <v>-17.5</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="25">
@@ -1782,7 +1782,7 @@
         <v>806</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1048</v>
+        <v>887</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>9.550000000000001</v>
@@ -1794,7 +1794,7 @@
         <v>7.8</v>
       </c>
       <c r="L25" t="n">
-        <v>-17.1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="26">
@@ -1830,7 +1830,7 @@
         <v>771</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1002</v>
+        <v>848</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>9.140000000000001</v>
@@ -1842,7 +1842,7 @@
         <v>7.9</v>
       </c>
       <c r="L26" t="n">
-        <v>-17</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="27">
@@ -1878,7 +1878,7 @@
         <v>837</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1088</v>
+        <v>921</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>9.960000000000001</v>
@@ -1890,7 +1890,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-16.7</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="28">
@@ -1926,7 +1926,7 @@
         <v>620</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>806</v>
+        <v>682</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>7.41</v>
@@ -1938,7 +1938,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>-16.4</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="29">
@@ -1974,7 +1974,7 @@
         <v>706</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>918</v>
+        <v>777</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>8.5</v>
@@ -1986,7 +1986,7 @@
         <v>9.6</v>
       </c>
       <c r="L29" t="n">
-        <v>-15.7</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="30">
@@ -2022,7 +2022,7 @@
         <v>725</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>942</v>
+        <v>798</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>8.74</v>
@@ -2034,7 +2034,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>-15.6</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="31">
@@ -2070,7 +2070,7 @@
         <v>921</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1197</v>
+        <v>1013</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>11.13</v>
@@ -2082,7 +2082,7 @@
         <v>10</v>
       </c>
       <c r="L31" t="n">
-        <v>-15.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2118,7 +2118,7 @@
         <v>677</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>880</v>
+        <v>745</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>8.34</v>
@@ -2130,7 +2130,7 @@
         <v>12.1</v>
       </c>
       <c r="L32" t="n">
-        <v>-13.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="33">
@@ -2166,7 +2166,7 @@
         <v>739</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>961</v>
+        <v>813</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>9.140000000000001</v>
@@ -2178,7 +2178,7 @@
         <v>12.6</v>
       </c>
       <c r="L33" t="n">
-        <v>-13.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="34">
@@ -2214,7 +2214,7 @@
         <v>935</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1216</v>
+        <v>1028</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>11.58</v>
@@ -2226,7 +2226,7 @@
         <v>12.7</v>
       </c>
       <c r="L34" t="n">
-        <v>-13.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="35">
@@ -2262,7 +2262,7 @@
         <v>993</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>1291</v>
+        <v>1092</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>12.31</v>
@@ -2274,7 +2274,7 @@
         <v>12.8</v>
       </c>
       <c r="L35" t="n">
-        <v>-13.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="36">
@@ -2310,7 +2310,7 @@
         <v>1032</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1342</v>
+        <v>1135</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>12.8</v>
@@ -2322,7 +2322,7 @@
         <v>12.9</v>
       </c>
       <c r="L36" t="n">
-        <v>-13.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="37">
@@ -2358,7 +2358,7 @@
         <v>693</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>901</v>
+        <v>762</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>8.6</v>
@@ -2370,7 +2370,7 @@
         <v>13</v>
       </c>
       <c r="L37" t="n">
-        <v>-13.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="38">
@@ -2406,7 +2406,7 @@
         <v>818</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1063</v>
+        <v>900</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>10.16</v>
@@ -2418,7 +2418,7 @@
         <v>13.1</v>
       </c>
       <c r="L38" t="n">
-        <v>-13</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="39">
@@ -2454,7 +2454,7 @@
         <v>620</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>806</v>
+        <v>682</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>7.73</v>
@@ -2466,7 +2466,7 @@
         <v>13.4</v>
       </c>
       <c r="L39" t="n">
-        <v>-12.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="40">
@@ -2502,7 +2502,7 @@
         <v>740</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>962</v>
+        <v>814</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>9.23</v>
@@ -2514,7 +2514,7 @@
         <v>13.5</v>
       </c>
       <c r="L40" t="n">
-        <v>-12.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="41">
@@ -2550,7 +2550,7 @@
         <v>1054</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>1370</v>
+        <v>1159</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>13.21</v>
@@ -2562,7 +2562,7 @@
         <v>14</v>
       </c>
       <c r="L41" t="n">
-        <v>-12.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="42">
@@ -2598,7 +2598,7 @@
         <v>745</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>968</v>
+        <v>820</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>9.35</v>
@@ -2610,7 +2610,7 @@
         <v>14.2</v>
       </c>
       <c r="L42" t="n">
-        <v>-12.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="43">
@@ -2646,7 +2646,7 @@
         <v>694</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>902</v>
+        <v>763</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>8.710000000000001</v>
@@ -2658,7 +2658,7 @@
         <v>14.3</v>
       </c>
       <c r="L43" t="n">
-        <v>-12.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="44">
@@ -2694,7 +2694,7 @@
         <v>806</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1048</v>
+        <v>887</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>10.16</v>
@@ -2706,7 +2706,7 @@
         <v>14.8</v>
       </c>
       <c r="L44" t="n">
-        <v>-11.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="45">
@@ -2742,7 +2742,7 @@
         <v>725</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>942</v>
+        <v>798</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>9.140000000000001</v>
@@ -2754,7 +2754,7 @@
         <v>14.8</v>
       </c>
       <c r="L45" t="n">
-        <v>-11.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="46">
@@ -2790,7 +2790,7 @@
         <v>741</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>963</v>
+        <v>815</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>9.380000000000001</v>
@@ -2802,7 +2802,7 @@
         <v>15.2</v>
       </c>
       <c r="L46" t="n">
-        <v>-11.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="47">
@@ -2838,7 +2838,7 @@
         <v>795</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>1034</v>
+        <v>875</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>10.07</v>
@@ -2850,7 +2850,7 @@
         <v>15.2</v>
       </c>
       <c r="L47" t="n">
-        <v>-11.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="48">
@@ -2886,7 +2886,7 @@
         <v>719</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>935</v>
+        <v>791</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>9.140000000000001</v>
@@ -2898,7 +2898,7 @@
         <v>15.7</v>
       </c>
       <c r="L48" t="n">
-        <v>-11</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="49">
@@ -2934,7 +2934,7 @@
         <v>638</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>829</v>
+        <v>702</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>8.130000000000001</v>
@@ -2946,7 +2946,7 @@
         <v>16</v>
       </c>
       <c r="L49" t="n">
-        <v>-10.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="50">
@@ -2982,7 +2982,7 @@
         <v>638</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>829</v>
+        <v>702</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>8.130000000000001</v>
@@ -2994,7 +2994,7 @@
         <v>16</v>
       </c>
       <c r="L50" t="n">
-        <v>-10.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="51">
@@ -3030,7 +3030,7 @@
         <v>725</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>942</v>
+        <v>798</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>9.26</v>
@@ -3042,7 +3042,7 @@
         <v>16.3</v>
       </c>
       <c r="L51" t="n">
-        <v>-10.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="52">
@@ -3078,7 +3078,7 @@
         <v>1399</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>1819</v>
+        <v>1539</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>17.88</v>
@@ -3090,7 +3090,7 @@
         <v>16.3</v>
       </c>
       <c r="L52" t="n">
-        <v>-10.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="53">
@@ -3126,7 +3126,7 @@
         <v>709</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>922</v>
+        <v>780</v>
       </c>
       <c r="I53" s="3" t="n">
         <v>9.07</v>
@@ -3138,7 +3138,7 @@
         <v>16.4</v>
       </c>
       <c r="L53" t="n">
-        <v>-10.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="54">
@@ -3174,7 +3174,7 @@
         <v>841</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>1093</v>
+        <v>925</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>10.77</v>
@@ -3186,7 +3186,7 @@
         <v>16.5</v>
       </c>
       <c r="L54" t="n">
-        <v>-10.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="55">
@@ -3222,7 +3222,7 @@
         <v>688</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>894</v>
+        <v>757</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>8.81</v>
@@ -3234,7 +3234,7 @@
         <v>16.6</v>
       </c>
       <c r="L55" t="n">
-        <v>-10.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="56">
@@ -3270,7 +3270,7 @@
         <v>697</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>906</v>
+        <v>767</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>8.94</v>
@@ -3282,7 +3282,7 @@
         <v>16.8</v>
       </c>
       <c r="L56" t="n">
-        <v>-10.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="57">
@@ -3318,7 +3318,7 @@
         <v>870</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>1131</v>
+        <v>957</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>11.19</v>
@@ -3330,7 +3330,7 @@
         <v>17</v>
       </c>
       <c r="L57" t="n">
-        <v>-10</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="58">
@@ -3366,7 +3366,7 @@
         <v>750</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>975</v>
+        <v>825</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>9.720000000000001</v>
@@ -3378,7 +3378,7 @@
         <v>18</v>
       </c>
       <c r="L58" t="n">
-        <v>-9.199999999999999</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="59">
@@ -3414,7 +3414,7 @@
         <v>690</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>897</v>
+        <v>759</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>8.94</v>
@@ -3426,7 +3426,7 @@
         <v>18</v>
       </c>
       <c r="L59" t="n">
-        <v>-9.300000000000001</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="60">
@@ -3462,7 +3462,7 @@
         <v>1002</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1303</v>
+        <v>1102</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>13</v>
@@ -3474,7 +3474,7 @@
         <v>18.1</v>
       </c>
       <c r="L60" t="n">
-        <v>-9.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="61">
@@ -3510,7 +3510,7 @@
         <v>508</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>660</v>
+        <v>559</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>6.62</v>
@@ -3522,7 +3522,7 @@
         <v>18.5</v>
       </c>
       <c r="L61" t="n">
-        <v>-8.800000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="62">
@@ -3558,7 +3558,7 @@
         <v>623</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>810</v>
+        <v>685</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>8.130000000000001</v>
@@ -3570,7 +3570,7 @@
         <v>18.8</v>
       </c>
       <c r="L62" t="n">
-        <v>-8.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -3606,7 +3606,7 @@
         <v>971</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1262</v>
+        <v>1068</v>
       </c>
       <c r="I63" s="3" t="n">
         <v>12.73</v>
@@ -3618,7 +3618,7 @@
         <v>19.3</v>
       </c>
       <c r="L63" t="n">
-        <v>-8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="64">
@@ -3654,7 +3654,7 @@
         <v>589</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>766</v>
+        <v>648</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>7.72</v>
@@ -3666,7 +3666,7 @@
         <v>19.4</v>
       </c>
       <c r="L64" t="n">
-        <v>-8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="65">
@@ -3702,7 +3702,7 @@
         <v>774</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>1006</v>
+        <v>851</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>10.16</v>
@@ -3714,7 +3714,7 @@
         <v>19.5</v>
       </c>
       <c r="L65" t="n">
-        <v>-8.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -3750,7 +3750,7 @@
         <v>851</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>1106</v>
+        <v>936</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>11.18</v>
@@ -3762,7 +3762,7 @@
         <v>19.5</v>
       </c>
       <c r="L66" t="n">
-        <v>-8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -3798,7 +3798,7 @@
         <v>1161</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1509</v>
+        <v>1277</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>15.24</v>
@@ -3810,7 +3810,7 @@
         <v>19.5</v>
       </c>
       <c r="L67" t="n">
-        <v>-8.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="68">
@@ -3846,7 +3846,7 @@
         <v>607</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>789</v>
+        <v>668</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>7.98</v>
@@ -3858,7 +3858,7 @@
         <v>19.6</v>
       </c>
       <c r="L68" t="n">
-        <v>-8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -3894,7 +3894,7 @@
         <v>896</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>1165</v>
+        <v>986</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>11.78</v>
@@ -3906,7 +3906,7 @@
         <v>19.6</v>
       </c>
       <c r="L69" t="n">
-        <v>-8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -3942,7 +3942,7 @@
         <v>657</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>854</v>
+        <v>723</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>8.65</v>
@@ -3954,7 +3954,7 @@
         <v>19.8</v>
       </c>
       <c r="L70" t="n">
-        <v>-7.8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="71">
@@ -3990,7 +3990,7 @@
         <v>529</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>688</v>
+        <v>582</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>6.97</v>
@@ -4002,7 +4002,7 @@
         <v>19.8</v>
       </c>
       <c r="L71" t="n">
-        <v>-7.8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="72">
@@ -4038,7 +4038,7 @@
         <v>694</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>902</v>
+        <v>763</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>9.15</v>
@@ -4050,7 +4050,7 @@
         <v>20</v>
       </c>
       <c r="L72" t="n">
-        <v>-7.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -4086,7 +4086,7 @@
         <v>676</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>879</v>
+        <v>744</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>8.92</v>
@@ -4098,7 +4098,7 @@
         <v>20.1</v>
       </c>
       <c r="L73" t="n">
-        <v>-7.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="74">
@@ -4132,7 +4132,7 @@
         <v>12958</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>16845</v>
+        <v>14254</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>172.66</v>
@@ -4144,7 +4144,7 @@
         <v>21.3</v>
       </c>
       <c r="L74" t="n">
-        <v>-6.7</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="75">
@@ -4178,7 +4178,7 @@
         <v>12958</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>16845</v>
+        <v>14254</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>172.66</v>
@@ -4190,7 +4190,7 @@
         <v>21.3</v>
       </c>
       <c r="L75" t="n">
-        <v>-6.7</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="76">
@@ -4226,7 +4226,7 @@
         <v>1036</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>1347</v>
+        <v>1140</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>13.82</v>
@@ -4238,7 +4238,7 @@
         <v>21.4</v>
       </c>
       <c r="L76" t="n">
-        <v>-6.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="77">
@@ -4274,7 +4274,7 @@
         <v>467</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>607</v>
+        <v>514</v>
       </c>
       <c r="I77" s="3" t="n">
         <v>6.28</v>
@@ -4286,7 +4286,7 @@
         <v>22.3</v>
       </c>
       <c r="L77" t="n">
-        <v>-5.9</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="78">
@@ -4322,7 +4322,7 @@
         <v>903</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>1174</v>
+        <v>993</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>12.24</v>
@@ -4334,7 +4334,7 @@
         <v>23.4</v>
       </c>
       <c r="L78" t="n">
-        <v>-5.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="79">
@@ -4370,7 +4370,7 @@
         <v>674</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>876</v>
+        <v>741</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>9.140000000000001</v>
@@ -4382,7 +4382,7 @@
         <v>23.4</v>
       </c>
       <c r="L79" t="n">
-        <v>-5</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="80">
@@ -4418,7 +4418,7 @@
         <v>674</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>876</v>
+        <v>741</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>9.140000000000001</v>
@@ -4430,7 +4430,7 @@
         <v>23.4</v>
       </c>
       <c r="L80" t="n">
-        <v>-5</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="81">
@@ -4466,7 +4466,7 @@
         <v>567</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>737</v>
+        <v>624</v>
       </c>
       <c r="I81" s="3" t="n">
         <v>7.69</v>
@@ -4478,7 +4478,7 @@
         <v>23.5</v>
       </c>
       <c r="L81" t="n">
-        <v>-5</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="82">
@@ -4514,7 +4514,7 @@
         <v>943</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>1226</v>
+        <v>1037</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>12.8</v>
@@ -4526,7 +4526,7 @@
         <v>23.5</v>
       </c>
       <c r="L82" t="n">
-        <v>-5</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="83">
@@ -4562,7 +4562,7 @@
         <v>896</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>1165</v>
+        <v>986</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>12.19</v>
@@ -4574,7 +4574,7 @@
         <v>23.8</v>
       </c>
       <c r="L83" t="n">
-        <v>-4.8</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="84">
@@ -4610,7 +4610,7 @@
         <v>821</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1067</v>
+        <v>903</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>11.18</v>
@@ -4622,7 +4622,7 @@
         <v>23.9</v>
       </c>
       <c r="L84" t="n">
-        <v>-4.7</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="85">
@@ -4658,7 +4658,7 @@
         <v>591</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>768</v>
+        <v>650</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>8.039999999999999</v>
@@ -4670,7 +4670,7 @@
         <v>23.9</v>
       </c>
       <c r="L85" t="n">
-        <v>-4.7</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="86">
@@ -4706,7 +4706,7 @@
         <v>446</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>580</v>
+        <v>491</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>6.09</v>
@@ -4718,7 +4718,7 @@
         <v>24.2</v>
       </c>
       <c r="L86" t="n">
-        <v>-4.5</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="87">
@@ -4754,7 +4754,7 @@
         <v>669</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>870</v>
+        <v>736</v>
       </c>
       <c r="I87" s="3" t="n">
         <v>9.140000000000001</v>
@@ -4766,7 +4766,7 @@
         <v>24.4</v>
       </c>
       <c r="L87" t="n">
-        <v>-4.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88">
@@ -4802,7 +4802,7 @@
         <v>564</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>733</v>
+        <v>620</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>7.72</v>
@@ -4814,7 +4814,7 @@
         <v>24.6</v>
       </c>
       <c r="L88" t="n">
-        <v>-4.1</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="89">
@@ -4850,7 +4850,7 @@
         <v>774</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>1006</v>
+        <v>851</v>
       </c>
       <c r="I89" s="3" t="n">
         <v>10.62</v>
@@ -4862,7 +4862,7 @@
         <v>24.8</v>
       </c>
       <c r="L89" t="n">
-        <v>-4</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="90">
@@ -4898,7 +4898,7 @@
         <v>596</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>775</v>
+        <v>656</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>8.18</v>
@@ -4910,7 +4910,7 @@
         <v>24.8</v>
       </c>
       <c r="L90" t="n">
-        <v>-4</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="91">
@@ -4946,7 +4946,7 @@
         <v>739</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>961</v>
+        <v>813</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>10.16</v>
@@ -4958,7 +4958,7 @@
         <v>25.2</v>
       </c>
       <c r="L91" t="n">
-        <v>-3.7</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="92">
@@ -4994,7 +4994,7 @@
         <v>620</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>806</v>
+        <v>682</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>8.539999999999999</v>
@@ -5006,7 +5006,7 @@
         <v>25.3</v>
       </c>
       <c r="L92" t="n">
-        <v>-3.6</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="93">
@@ -5042,7 +5042,7 @@
         <v>806</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>1048</v>
+        <v>887</v>
       </c>
       <c r="I93" s="3" t="n">
         <v>11.18</v>
@@ -5054,7 +5054,7 @@
         <v>26.2</v>
       </c>
       <c r="L93" t="n">
-        <v>-3</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="94">
@@ -5090,7 +5090,7 @@
         <v>774</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>1006</v>
+        <v>851</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>10.78</v>
@@ -5102,7 +5102,7 @@
         <v>26.7</v>
       </c>
       <c r="L94" t="n">
-        <v>-2.5</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="95">
@@ -5138,7 +5138,7 @@
         <v>603</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>784</v>
+        <v>663</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>8.41</v>
@@ -5150,7 +5150,7 @@
         <v>26.9</v>
       </c>
       <c r="L95" t="n">
-        <v>-2.4</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="96">
@@ -5186,7 +5186,7 @@
         <v>597</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>776</v>
+        <v>657</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>8.34</v>
@@ -5198,7 +5198,7 @@
         <v>27.1</v>
       </c>
       <c r="L96" t="n">
-        <v>-2.2</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="97">
@@ -5234,7 +5234,7 @@
         <v>774</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>1006</v>
+        <v>851</v>
       </c>
       <c r="I97" s="3" t="n">
         <v>10.84</v>
@@ -5246,7 +5246,7 @@
         <v>27.4</v>
       </c>
       <c r="L97" t="n">
-        <v>-2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="98">
@@ -5282,7 +5282,7 @@
         <v>608</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>790</v>
+        <v>669</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>8.539999999999999</v>
@@ -5294,7 +5294,7 @@
         <v>27.8</v>
       </c>
       <c r="L98" t="n">
-        <v>-1.6</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="99">
@@ -5330,7 +5330,7 @@
         <v>1354</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>1760</v>
+        <v>1489</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>19.03</v>
@@ -5342,7 +5342,7 @@
         <v>27.9</v>
       </c>
       <c r="L99" t="n">
-        <v>-1.6</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="100">
@@ -5378,7 +5378,7 @@
         <v>721</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>937</v>
+        <v>793</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>10.16</v>
@@ -5390,7 +5390,7 @@
         <v>28.3</v>
       </c>
       <c r="L100" t="n">
-        <v>-1.3</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="101">
@@ -5426,7 +5426,7 @@
         <v>657</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>854</v>
+        <v>723</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>9.34</v>
@@ -5438,7 +5438,7 @@
         <v>29.4</v>
       </c>
       <c r="L101" t="n">
-        <v>-0.5</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="102">
@@ -5474,7 +5474,7 @@
         <v>806</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>1048</v>
+        <v>887</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>11.47</v>
@@ -5486,7 +5486,7 @@
         <v>29.5</v>
       </c>
       <c r="L102" t="n">
-        <v>-0.4</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="103">
@@ -5522,7 +5522,7 @@
         <v>806</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>1048</v>
+        <v>887</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>11.49</v>
@@ -5534,7 +5534,7 @@
         <v>29.8</v>
       </c>
       <c r="L103" t="n">
-        <v>-0.2</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="104">
@@ -5570,7 +5570,7 @@
         <v>479</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>623</v>
+        <v>527</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>6.84</v>
@@ -5582,7 +5582,7 @@
         <v>29.9</v>
       </c>
       <c r="L104" t="n">
-        <v>-0.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105">
@@ -5618,7 +5618,7 @@
         <v>822</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>1069</v>
+        <v>904</v>
       </c>
       <c r="I105" s="3" t="n">
         <v>11.78</v>
@@ -5630,7 +5630,7 @@
         <v>30.4</v>
       </c>
       <c r="L105" t="n">
-        <v>0.3</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="106">
@@ -5666,7 +5666,7 @@
         <v>822</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>1069</v>
+        <v>904</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>11.78</v>
@@ -5678,7 +5678,7 @@
         <v>30.4</v>
       </c>
       <c r="L106" t="n">
-        <v>0.3</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="107">
@@ -5714,7 +5714,7 @@
         <v>822</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>1069</v>
+        <v>904</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>11.78</v>
@@ -5726,7 +5726,7 @@
         <v>30.4</v>
       </c>
       <c r="L107" t="n">
-        <v>0.3</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="108">
@@ -5762,7 +5762,7 @@
         <v>709</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>922</v>
+        <v>780</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>10.16</v>
@@ -5774,7 +5774,7 @@
         <v>30.5</v>
       </c>
       <c r="L108" t="n">
-        <v>0.3</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="109">
@@ -5810,7 +5810,7 @@
         <v>567</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>737</v>
+        <v>624</v>
       </c>
       <c r="I109" s="3" t="n">
         <v>8.130000000000001</v>
@@ -5822,7 +5822,7 @@
         <v>30.5</v>
       </c>
       <c r="L109" t="n">
-        <v>0.4</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="110">
@@ -5858,7 +5858,7 @@
         <v>635</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>826</v>
+        <v>698</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>9.140000000000001</v>
@@ -5870,7 +5870,7 @@
         <v>31</v>
       </c>
       <c r="L110" t="n">
-        <v>0.7</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="111">
@@ -5906,7 +5906,7 @@
         <v>676</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>879</v>
+        <v>744</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>9.75</v>
@@ -5918,7 +5918,7 @@
         <v>31.2</v>
       </c>
       <c r="L111" t="n">
-        <v>0.9</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="112">
@@ -5954,7 +5954,7 @@
         <v>745</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>968</v>
+        <v>820</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>10.77</v>
@@ -5966,7 +5966,7 @@
         <v>31.5</v>
       </c>
       <c r="L112" t="n">
-        <v>1.2</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="113">
@@ -6002,7 +6002,7 @@
         <v>631</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>820</v>
+        <v>694</v>
       </c>
       <c r="I113" s="3" t="n">
         <v>9.140000000000001</v>
@@ -6014,7 +6014,7 @@
         <v>31.9</v>
       </c>
       <c r="L113" t="n">
-        <v>1.5</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="114">
@@ -6050,7 +6050,7 @@
         <v>747</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>971</v>
+        <v>822</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>10.82</v>
@@ -6062,7 +6062,7 @@
         <v>31.9</v>
       </c>
       <c r="L114" t="n">
-        <v>1.4</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="115">
@@ -6098,7 +6098,7 @@
         <v>729</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>948</v>
+        <v>802</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>10.57</v>
@@ -6110,7 +6110,7 @@
         <v>32</v>
       </c>
       <c r="L115" t="n">
-        <v>1.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116">
@@ -6146,7 +6146,7 @@
         <v>613</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>797</v>
+        <v>674</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>8.9</v>
@@ -6158,7 +6158,7 @@
         <v>32.1</v>
       </c>
       <c r="L116" t="n">
-        <v>1.6</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="117">
@@ -6194,7 +6194,7 @@
         <v>770</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>1001</v>
+        <v>847</v>
       </c>
       <c r="I117" s="3" t="n">
         <v>11.18</v>
@@ -6206,7 +6206,7 @@
         <v>32.1</v>
       </c>
       <c r="L117" t="n">
-        <v>1.6</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="118">
@@ -6242,7 +6242,7 @@
         <v>1228</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>1596</v>
+        <v>1351</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>17.84</v>
@@ -6254,7 +6254,7 @@
         <v>32.2</v>
       </c>
       <c r="L118" t="n">
-        <v>1.7</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="119">
@@ -6290,7 +6290,7 @@
         <v>604</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>785</v>
+        <v>664</v>
       </c>
       <c r="I119" s="3" t="n">
         <v>8.789999999999999</v>
@@ -6302,7 +6302,7 @@
         <v>32.5</v>
       </c>
       <c r="L119" t="n">
-        <v>1.9</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="120">
@@ -6338,7 +6338,7 @@
         <v>873</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>1135</v>
+        <v>960</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>12.73</v>
@@ -6350,7 +6350,7 @@
         <v>32.6</v>
       </c>
       <c r="L120" t="n">
-        <v>2</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="121">
@@ -6386,7 +6386,7 @@
         <v>770</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>1001</v>
+        <v>847</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>11.25</v>
@@ -6398,7 +6398,7 @@
         <v>33</v>
       </c>
       <c r="L121" t="n">
-        <v>2.3</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="122">
@@ -6434,7 +6434,7 @@
         <v>555</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>722</v>
+        <v>610</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>8.130000000000001</v>
@@ -6446,7 +6446,7 @@
         <v>33.3</v>
       </c>
       <c r="L122" t="n">
-        <v>2.5</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="123">
@@ -6482,7 +6482,7 @@
         <v>664</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>863</v>
+        <v>730</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>9.75</v>
@@ -6494,7 +6494,7 @@
         <v>33.6</v>
       </c>
       <c r="L123" t="n">
-        <v>2.8</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="124">
@@ -6530,7 +6530,7 @@
         <v>1173</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>1525</v>
+        <v>1290</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>17.29</v>
@@ -6542,7 +6542,7 @@
         <v>34.1</v>
       </c>
       <c r="L124" t="n">
-        <v>3.1</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="125">
@@ -6578,7 +6578,7 @@
         <v>620</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>806</v>
+        <v>682</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>9.140000000000001</v>
@@ -6590,7 +6590,7 @@
         <v>34.2</v>
       </c>
       <c r="L125" t="n">
-        <v>3.2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126">
@@ -6626,7 +6626,7 @@
         <v>739</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>961</v>
+        <v>813</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>10.93</v>
@@ -6638,7 +6638,7 @@
         <v>34.6</v>
       </c>
       <c r="L126" t="n">
-        <v>3.5</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="127">
@@ -6674,7 +6674,7 @@
         <v>873</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>1135</v>
+        <v>960</v>
       </c>
       <c r="I127" s="3" t="n">
         <v>12.92</v>
@@ -6686,7 +6686,7 @@
         <v>34.7</v>
       </c>
       <c r="L127" t="n">
-        <v>3.6</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="128">
@@ -6722,7 +6722,7 @@
         <v>548</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>712</v>
+        <v>603</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>8.130000000000001</v>
@@ -6734,7 +6734,7 @@
         <v>35</v>
       </c>
       <c r="L128" t="n">
-        <v>3.9</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="129">
@@ -6770,7 +6770,7 @@
         <v>603</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>784</v>
+        <v>663</v>
       </c>
       <c r="I129" s="3" t="n">
         <v>8.94</v>
@@ -6782,7 +6782,7 @@
         <v>35</v>
       </c>
       <c r="L129" t="n">
-        <v>3.8</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="130">
@@ -6818,7 +6818,7 @@
         <v>479</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>623</v>
+        <v>527</v>
       </c>
       <c r="I130" s="3" t="n">
         <v>7.11</v>
@@ -6830,7 +6830,7 @@
         <v>35.1</v>
       </c>
       <c r="L130" t="n">
-        <v>3.9</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="131">
@@ -6866,7 +6866,7 @@
         <v>825</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>1072</v>
+        <v>908</v>
       </c>
       <c r="I131" s="3" t="n">
         <v>12.28</v>
@@ -6878,7 +6878,7 @@
         <v>35.4</v>
       </c>
       <c r="L131" t="n">
-        <v>4.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132">
@@ -6914,7 +6914,7 @@
         <v>614</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>798</v>
+        <v>675</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>9.140000000000001</v>
@@ -6926,7 +6926,7 @@
         <v>35.5</v>
       </c>
       <c r="L132" t="n">
-        <v>4.3</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="133">
@@ -6962,7 +6962,7 @@
         <v>544</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>707</v>
+        <v>598</v>
       </c>
       <c r="I133" s="3" t="n">
         <v>8.130000000000001</v>
@@ -6974,7 +6974,7 @@
         <v>36</v>
       </c>
       <c r="L133" t="n">
-        <v>4.7</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="134">
@@ -7010,7 +7010,7 @@
         <v>1220</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>1586</v>
+        <v>1342</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>18.24</v>
@@ -7022,7 +7022,7 @@
         <v>36.1</v>
       </c>
       <c r="L134" t="n">
-        <v>4.7</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="135">
@@ -7058,7 +7058,7 @@
         <v>814</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>1058</v>
+        <v>895</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>12.19</v>
@@ -7070,7 +7070,7 @@
         <v>36.2</v>
       </c>
       <c r="L135" t="n">
-        <v>4.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="136">
@@ -7106,7 +7106,7 @@
         <v>729</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>948</v>
+        <v>802</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>10.95</v>
@@ -7118,7 +7118,7 @@
         <v>36.6</v>
       </c>
       <c r="L136" t="n">
-        <v>5.1</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="137">
@@ -7154,7 +7154,7 @@
         <v>757</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>984</v>
+        <v>833</v>
       </c>
       <c r="I137" s="3" t="n">
         <v>11.38</v>
@@ -7166,7 +7166,7 @@
         <v>36.9</v>
       </c>
       <c r="L137" t="n">
-        <v>5.3</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="138">
@@ -7202,7 +7202,7 @@
         <v>781</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>1015</v>
+        <v>859</v>
       </c>
       <c r="I138" s="3" t="n">
         <v>11.78</v>
@@ -7214,7 +7214,7 @@
         <v>37.3</v>
       </c>
       <c r="L138" t="n">
-        <v>5.6</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="139">
@@ -7250,7 +7250,7 @@
         <v>337</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>438</v>
+        <v>371</v>
       </c>
       <c r="I139" s="3" t="n">
         <v>5.09</v>
@@ -7262,7 +7262,7 @@
         <v>37.4</v>
       </c>
       <c r="L139" t="n">
-        <v>5.7</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="140">
@@ -7298,7 +7298,7 @@
         <v>525</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>682</v>
+        <v>578</v>
       </c>
       <c r="I140" s="3" t="n">
         <v>7.93</v>
@@ -7310,7 +7310,7 @@
         <v>37.5</v>
       </c>
       <c r="L140" t="n">
-        <v>5.9</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="141">
@@ -7346,7 +7346,7 @@
         <v>1008</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>1310</v>
+        <v>1109</v>
       </c>
       <c r="I141" s="3" t="n">
         <v>15.24</v>
@@ -7358,7 +7358,7 @@
         <v>37.6</v>
       </c>
       <c r="L141" t="n">
-        <v>5.9</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="142">
@@ -7394,7 +7394,7 @@
         <v>774</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>1006</v>
+        <v>851</v>
       </c>
       <c r="I142" s="3" t="n">
         <v>11.74</v>
@@ -7406,7 +7406,7 @@
         <v>38</v>
       </c>
       <c r="L142" t="n">
-        <v>6.2</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="143">
@@ -7442,7 +7442,7 @@
         <v>868</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>1128</v>
+        <v>955</v>
       </c>
       <c r="I143" s="3" t="n">
         <v>13.21</v>
@@ -7454,7 +7454,7 @@
         <v>38.5</v>
       </c>
       <c r="L143" t="n">
-        <v>6.6</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="144">
@@ -7490,7 +7490,7 @@
         <v>521</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>677</v>
+        <v>573</v>
       </c>
       <c r="I144" s="3" t="n">
         <v>7.93</v>
@@ -7502,7 +7502,7 @@
         <v>38.6</v>
       </c>
       <c r="L144" t="n">
-        <v>6.6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="145">
@@ -7538,7 +7538,7 @@
         <v>600</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>780</v>
+        <v>660</v>
       </c>
       <c r="I145" s="3" t="n">
         <v>9.140000000000001</v>
@@ -7550,7 +7550,7 @@
         <v>38.7</v>
       </c>
       <c r="L145" t="n">
-        <v>6.7</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="146">
@@ -7586,7 +7586,7 @@
         <v>733</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>953</v>
+        <v>806</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>11.18</v>
@@ -7598,7 +7598,7 @@
         <v>38.7</v>
       </c>
       <c r="L146" t="n">
-        <v>6.7</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="147">
@@ -7634,7 +7634,7 @@
         <v>1220</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>1586</v>
+        <v>1342</v>
       </c>
       <c r="I147" s="3" t="n">
         <v>18.63</v>
@@ -7646,7 +7646,7 @@
         <v>38.9</v>
       </c>
       <c r="L147" t="n">
-        <v>6.9</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="148">
@@ -7682,7 +7682,7 @@
         <v>745</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>968</v>
+        <v>820</v>
       </c>
       <c r="I148" s="3" t="n">
         <v>11.38</v>
@@ -7694,7 +7694,7 @@
         <v>39.1</v>
       </c>
       <c r="L148" t="n">
-        <v>7</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="149">
@@ -7730,7 +7730,7 @@
         <v>774</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>1006</v>
+        <v>851</v>
       </c>
       <c r="I149" s="3" t="n">
         <v>11.85</v>
@@ -7742,7 +7742,7 @@
         <v>39.3</v>
       </c>
       <c r="L149" t="n">
-        <v>7.2</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="150">
@@ -7778,7 +7778,7 @@
         <v>597</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>776</v>
+        <v>657</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>9.140000000000001</v>
@@ -7790,7 +7790,7 @@
         <v>39.4</v>
       </c>
       <c r="L150" t="n">
-        <v>7.2</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="151">
@@ -7826,7 +7826,7 @@
         <v>729</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>948</v>
+        <v>802</v>
       </c>
       <c r="I151" s="3" t="n">
         <v>11.28</v>
@@ -7838,7 +7838,7 @@
         <v>40.7</v>
       </c>
       <c r="L151" t="n">
-        <v>8.199999999999999</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="152">
@@ -7874,7 +7874,7 @@
         <v>469</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>610</v>
+        <v>516</v>
       </c>
       <c r="I152" s="3" t="n">
         <v>7.32</v>
@@ -7886,7 +7886,7 @@
         <v>42</v>
       </c>
       <c r="L152" t="n">
-        <v>9.199999999999999</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="153">
@@ -7922,7 +7922,7 @@
         <v>493</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>641</v>
+        <v>542</v>
       </c>
       <c r="I153" s="3" t="n">
         <v>7.72</v>
@@ -7934,7 +7934,7 @@
         <v>42.6</v>
       </c>
       <c r="L153" t="n">
-        <v>9.699999999999999</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="154">
@@ -7970,7 +7970,7 @@
         <v>709</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>922</v>
+        <v>780</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>11.18</v>
@@ -7982,7 +7982,7 @@
         <v>43.4</v>
       </c>
       <c r="L154" t="n">
-        <v>10.3</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="155">
@@ -8018,7 +8018,7 @@
         <v>705</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>916</v>
+        <v>776</v>
       </c>
       <c r="I155" s="3" t="n">
         <v>11.18</v>
@@ -8030,7 +8030,7 @@
         <v>44.3</v>
       </c>
       <c r="L155" t="n">
-        <v>11</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="156">
@@ -8066,7 +8066,7 @@
         <v>813</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>1057</v>
+        <v>894</v>
       </c>
       <c r="I156" s="3" t="n">
         <v>12.92</v>
@@ -8078,7 +8078,7 @@
         <v>44.6</v>
       </c>
       <c r="L156" t="n">
-        <v>11.3</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="157">
@@ -8114,7 +8114,7 @@
         <v>1220</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>1586</v>
+        <v>1342</v>
       </c>
       <c r="I157" s="3" t="n">
         <v>19.56</v>
@@ -8126,7 +8126,7 @@
         <v>45.9</v>
       </c>
       <c r="L157" t="n">
-        <v>12.2</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="158">
@@ -8162,7 +8162,7 @@
         <v>558</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>725</v>
+        <v>614</v>
       </c>
       <c r="I158" s="3" t="n">
         <v>8.94</v>
@@ -8174,7 +8174,7 @@
         <v>45.9</v>
       </c>
       <c r="L158" t="n">
-        <v>12.3</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="159">
@@ -8210,7 +8210,7 @@
         <v>502</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>653</v>
+        <v>552</v>
       </c>
       <c r="I159" s="3" t="n">
         <v>8.050000000000001</v>
@@ -8222,7 +8222,7 @@
         <v>46</v>
       </c>
       <c r="L159" t="n">
-        <v>12.3</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="160">
@@ -8258,7 +8258,7 @@
         <v>722</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>939</v>
+        <v>794</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>11.59</v>
@@ -8270,7 +8270,7 @@
         <v>46.1</v>
       </c>
       <c r="L160" t="n">
-        <v>12.4</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="161">
@@ -8306,7 +8306,7 @@
         <v>1040</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>1352</v>
+        <v>1144</v>
       </c>
       <c r="I161" s="3" t="n">
         <v>16.72</v>
@@ -8318,7 +8318,7 @@
         <v>46.3</v>
       </c>
       <c r="L161" t="n">
-        <v>12.6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="162">
@@ -8354,7 +8354,7 @@
         <v>922</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>1199</v>
+        <v>1014</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>14.83</v>
@@ -8366,7 +8366,7 @@
         <v>46.4</v>
       </c>
       <c r="L162" t="n">
-        <v>12.6</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="163">
@@ -8402,7 +8402,7 @@
         <v>593</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>771</v>
+        <v>652</v>
       </c>
       <c r="I163" s="3" t="n">
         <v>9.550000000000001</v>
@@ -8414,7 +8414,7 @@
         <v>46.5</v>
       </c>
       <c r="L163" t="n">
-        <v>12.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="164">
@@ -8450,7 +8450,7 @@
         <v>567</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>737</v>
+        <v>624</v>
       </c>
       <c r="I164" s="3" t="n">
         <v>9.140000000000001</v>
@@ -8462,7 +8462,7 @@
         <v>46.7</v>
       </c>
       <c r="L164" t="n">
-        <v>12.9</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="165">
@@ -8498,7 +8498,7 @@
         <v>433</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>563</v>
+        <v>476</v>
       </c>
       <c r="I165" s="3" t="n">
         <v>6.98</v>
@@ -8510,7 +8510,7 @@
         <v>46.7</v>
       </c>
       <c r="L165" t="n">
-        <v>12.8</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="166">
@@ -8546,7 +8546,7 @@
         <v>567</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>737</v>
+        <v>624</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>9.140000000000001</v>
@@ -8558,7 +8558,7 @@
         <v>46.7</v>
       </c>
       <c r="L166" t="n">
-        <v>12.9</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="167">
@@ -8594,7 +8594,7 @@
         <v>557</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>724</v>
+        <v>613</v>
       </c>
       <c r="I167" s="3" t="n">
         <v>9.02</v>
@@ -8606,7 +8606,7 @@
         <v>47.4</v>
       </c>
       <c r="L167" t="n">
-        <v>13.4</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="168">
@@ -8642,7 +8642,7 @@
         <v>501</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>651</v>
+        <v>551</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>8.130000000000001</v>
@@ -8654,7 +8654,7 @@
         <v>47.7</v>
       </c>
       <c r="L168" t="n">
-        <v>13.7</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="169">
@@ -8690,7 +8690,7 @@
         <v>560</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>728</v>
+        <v>616</v>
       </c>
       <c r="I169" s="3" t="n">
         <v>9.109999999999999</v>
@@ -8702,7 +8702,7 @@
         <v>48</v>
       </c>
       <c r="L169" t="n">
-        <v>13.9</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="170">
@@ -8738,7 +8738,7 @@
         <v>622</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>809</v>
+        <v>684</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>10.16</v>
@@ -8750,7 +8750,7 @@
         <v>48.7</v>
       </c>
       <c r="L170" t="n">
-        <v>14.3</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="171">
@@ -8786,7 +8786,7 @@
         <v>393</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>511</v>
+        <v>432</v>
       </c>
       <c r="I171" s="3" t="n">
         <v>6.44</v>
@@ -8798,7 +8798,7 @@
         <v>49.1</v>
       </c>
       <c r="L171" t="n">
-        <v>14.7</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="172">
@@ -8834,7 +8834,7 @@
         <v>451</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>586</v>
+        <v>496</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>7.4</v>
@@ -8846,7 +8846,7 @@
         <v>49.2</v>
       </c>
       <c r="L172" t="n">
-        <v>14.8</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="173">
@@ -8882,7 +8882,7 @@
         <v>335</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>436</v>
+        <v>369</v>
       </c>
       <c r="I173" s="3" t="n">
         <v>5.49</v>
@@ -8894,7 +8894,7 @@
         <v>49.3</v>
       </c>
       <c r="L173" t="n">
-        <v>14.7</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="174">
@@ -8930,7 +8930,7 @@
         <v>458</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>595</v>
+        <v>504</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>7.52</v>
@@ -8942,7 +8942,7 @@
         <v>49.3</v>
       </c>
       <c r="L174" t="n">
-        <v>15</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="175">
@@ -8978,7 +8978,7 @@
         <v>557</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>724</v>
+        <v>613</v>
       </c>
       <c r="I175" s="3" t="n">
         <v>9.140000000000001</v>
@@ -8990,7 +8990,7 @@
         <v>49.4</v>
       </c>
       <c r="L175" t="n">
-        <v>14.9</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="176">
@@ -9026,7 +9026,7 @@
         <v>604</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>785</v>
+        <v>664</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>9.94</v>
@@ -9038,7 +9038,7 @@
         <v>49.8</v>
       </c>
       <c r="L176" t="n">
-        <v>15.3</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="177">
@@ -9074,7 +9074,7 @@
         <v>674</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>876</v>
+        <v>741</v>
       </c>
       <c r="I177" s="3" t="n">
         <v>11.18</v>
@@ -9086,7 +9086,7 @@
         <v>50.9</v>
       </c>
       <c r="L177" t="n">
-        <v>16.1</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="178">
@@ -9122,7 +9122,7 @@
         <v>694</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>902</v>
+        <v>763</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>11.53</v>
@@ -9134,7 +9134,7 @@
         <v>51.2</v>
       </c>
       <c r="L178" t="n">
-        <v>16.3</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="179">
@@ -9170,7 +9170,7 @@
         <v>1402</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>1823</v>
+        <v>1542</v>
       </c>
       <c r="I179" s="3" t="n">
         <v>23.37</v>
@@ -9182,7 +9182,7 @@
         <v>51.7</v>
       </c>
       <c r="L179" t="n">
-        <v>16.7</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="180">
@@ -9218,7 +9218,7 @@
         <v>558</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>725</v>
+        <v>614</v>
       </c>
       <c r="I180" s="3" t="n">
         <v>9.31</v>
@@ -9230,7 +9230,7 @@
         <v>51.8</v>
       </c>
       <c r="L180" t="n">
-        <v>16.8</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="181">
@@ -9266,7 +9266,7 @@
         <v>821</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>1067</v>
+        <v>903</v>
       </c>
       <c r="I181" s="3" t="n">
         <v>13.82</v>
@@ -9278,7 +9278,7 @@
         <v>53.2</v>
       </c>
       <c r="L181" t="n">
-        <v>17.9</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="182">
@@ -9314,7 +9314,7 @@
         <v>541</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>703</v>
+        <v>595</v>
       </c>
       <c r="I182" s="3" t="n">
         <v>9.140000000000001</v>
@@ -9326,7 +9326,7 @@
         <v>53.8</v>
       </c>
       <c r="L182" t="n">
-        <v>18.3</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="183">
@@ -9362,7 +9362,7 @@
         <v>391</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>508</v>
+        <v>430</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>6.62</v>
@@ -9374,7 +9374,7 @@
         <v>54</v>
       </c>
       <c r="L183" t="n">
-        <v>18.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="184">
@@ -9410,7 +9410,7 @@
         <v>575</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>748</v>
+        <v>632</v>
       </c>
       <c r="I184" s="3" t="n">
         <v>9.75</v>
@@ -9422,7 +9422,7 @@
         <v>54.3</v>
       </c>
       <c r="L184" t="n">
-        <v>18.6</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="185">
@@ -9458,7 +9458,7 @@
         <v>538</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>699</v>
+        <v>592</v>
       </c>
       <c r="I185" s="3" t="n">
         <v>9.140000000000001</v>
@@ -9470,7 +9470,7 @@
         <v>54.6</v>
       </c>
       <c r="L185" t="n">
-        <v>19</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="186">
@@ -9506,7 +9506,7 @@
         <v>347</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>451</v>
+        <v>382</v>
       </c>
       <c r="I186" s="3" t="n">
         <v>5.97</v>
@@ -9518,7 +9518,7 @@
         <v>56.5</v>
       </c>
       <c r="L186" t="n">
-        <v>20.4</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="187">
@@ -9554,7 +9554,7 @@
         <v>564</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>733</v>
+        <v>620</v>
       </c>
       <c r="I187" s="3" t="n">
         <v>9.75</v>
@@ -9566,7 +9566,7 @@
         <v>57.3</v>
       </c>
       <c r="L187" t="n">
-        <v>21</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="188">
@@ -9602,7 +9602,7 @@
         <v>446</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>580</v>
+        <v>491</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>7.72</v>
@@ -9614,7 +9614,7 @@
         <v>57.6</v>
       </c>
       <c r="L188" t="n">
-        <v>21.2</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="189">
@@ -9650,7 +9650,7 @@
         <v>597</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>776</v>
+        <v>657</v>
       </c>
       <c r="I189" s="3" t="n">
         <v>10.39</v>
@@ -9662,7 +9662,7 @@
         <v>58.3</v>
       </c>
       <c r="L189" t="n">
-        <v>21.8</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="190">
@@ -9698,7 +9698,7 @@
         <v>416</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>541</v>
+        <v>458</v>
       </c>
       <c r="I190" s="3" t="n">
         <v>7.31</v>
@@ -9710,7 +9710,7 @@
         <v>59.9</v>
       </c>
       <c r="L190" t="n">
-        <v>22.9</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="191">
@@ -9746,7 +9746,7 @@
         <v>635</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>826</v>
+        <v>698</v>
       </c>
       <c r="I191" s="3" t="n">
         <v>11.18</v>
@@ -9758,7 +9758,7 @@
         <v>60.2</v>
       </c>
       <c r="L191" t="n">
-        <v>23.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="192">
@@ -9794,7 +9794,7 @@
         <v>460</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>598</v>
+        <v>506</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>8.130000000000001</v>
@@ -9806,7 +9806,7 @@
         <v>60.9</v>
       </c>
       <c r="L192" t="n">
-        <v>23.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="193">
@@ -9842,7 +9842,7 @@
         <v>627</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>815</v>
+        <v>690</v>
       </c>
       <c r="I193" s="3" t="n">
         <v>11.18</v>
@@ -9854,7 +9854,7 @@
         <v>62.2</v>
       </c>
       <c r="L193" t="n">
-        <v>24.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="194">
@@ -9890,7 +9890,7 @@
         <v>416</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>541</v>
+        <v>458</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>7.46</v>
@@ -9902,7 +9902,7 @@
         <v>63.2</v>
       </c>
       <c r="L194" t="n">
-        <v>25.5</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="195">
@@ -9938,7 +9938,7 @@
         <v>451</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>586</v>
+        <v>496</v>
       </c>
       <c r="I195" s="3" t="n">
         <v>8.130000000000001</v>
@@ -9950,7 +9950,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="L195" t="n">
-        <v>26.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="196">
@@ -9986,7 +9986,7 @@
         <v>580</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>754</v>
+        <v>638</v>
       </c>
       <c r="I196" s="3" t="n">
         <v>10.57</v>
@@ -9998,7 +9998,7 @@
         <v>65.90000000000001</v>
       </c>
       <c r="L196" t="n">
-        <v>27.6</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="197">
@@ -10034,7 +10034,7 @@
         <v>496</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>645</v>
+        <v>546</v>
       </c>
       <c r="I197" s="3" t="n">
         <v>9.140000000000001</v>
@@ -10046,7 +10046,7 @@
         <v>67.7</v>
       </c>
       <c r="L197" t="n">
-        <v>29</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="198">
@@ -10082,7 +10082,7 @@
         <v>496</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>645</v>
+        <v>546</v>
       </c>
       <c r="I198" s="3" t="n">
         <v>9.140000000000001</v>
@@ -10094,7 +10094,7 @@
         <v>67.7</v>
       </c>
       <c r="L198" t="n">
-        <v>29</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="199">
@@ -10130,7 +10130,7 @@
         <v>627</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>815</v>
+        <v>690</v>
       </c>
       <c r="I199" s="3" t="n">
         <v>11.59</v>
@@ -10142,7 +10142,7 @@
         <v>68.3</v>
       </c>
       <c r="L199" t="n">
-        <v>29.4</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="200">
@@ -10178,7 +10178,7 @@
         <v>582</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>757</v>
+        <v>640</v>
       </c>
       <c r="I200" s="3" t="n">
         <v>10.77</v>
@@ -10190,7 +10190,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="L200" t="n">
-        <v>29.5</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="201">
@@ -10226,7 +10226,7 @@
         <v>411</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>534</v>
+        <v>452</v>
       </c>
       <c r="I201" s="3" t="n">
         <v>7.72</v>
@@ -10238,7 +10238,7 @@
         <v>71</v>
       </c>
       <c r="L201" t="n">
-        <v>31.6</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="202">
@@ -10274,7 +10274,7 @@
         <v>627</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>815</v>
+        <v>690</v>
       </c>
       <c r="I202" s="3" t="n">
         <v>11.78</v>
@@ -10286,7 +10286,7 @@
         <v>71</v>
       </c>
       <c r="L202" t="n">
-        <v>31.5</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="203">
@@ -10322,7 +10322,7 @@
         <v>1467</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>1907</v>
+        <v>1614</v>
       </c>
       <c r="I203" s="3" t="n">
         <v>27.77</v>
@@ -10334,7 +10334,7 @@
         <v>72.3</v>
       </c>
       <c r="L203" t="n">
-        <v>32.5</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="204">
@@ -10370,7 +10370,7 @@
         <v>627</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>815</v>
+        <v>690</v>
       </c>
       <c r="I204" s="3" t="n">
         <v>11.98</v>
@@ -10382,7 +10382,7 @@
         <v>73.8</v>
       </c>
       <c r="L204" t="n">
-        <v>33.7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="205">
@@ -10418,7 +10418,7 @@
         <v>423</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>550</v>
+        <v>465</v>
       </c>
       <c r="I205" s="3" t="n">
         <v>8.130000000000001</v>
@@ -10430,7 +10430,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="L205" t="n">
-        <v>34.5</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="206">
@@ -10466,7 +10466,7 @@
         <v>603</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>784</v>
+        <v>663</v>
       </c>
       <c r="I206" s="3" t="n">
         <v>11.59</v>
@@ -10478,7 +10478,7 @@
         <v>75</v>
       </c>
       <c r="L206" t="n">
-        <v>34.6</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="207">
@@ -10514,7 +10514,7 @@
         <v>369</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>480</v>
+        <v>406</v>
       </c>
       <c r="I207" s="3" t="n">
         <v>7.11</v>
@@ -10526,7 +10526,7 @@
         <v>75.3</v>
       </c>
       <c r="L207" t="n">
-        <v>34.8</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="208">
@@ -10562,7 +10562,7 @@
         <v>516</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>671</v>
+        <v>568</v>
       </c>
       <c r="I208" s="3" t="n">
         <v>10.16</v>
@@ -10574,7 +10574,7 @@
         <v>79.3</v>
       </c>
       <c r="L208" t="n">
-        <v>37.9</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="209">
@@ -10610,7 +10610,7 @@
         <v>358</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>465</v>
+        <v>394</v>
       </c>
       <c r="I209" s="3" t="n">
         <v>7.11</v>
@@ -10622,7 +10622,7 @@
         <v>80.7</v>
       </c>
       <c r="L209" t="n">
-        <v>39.1</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="210">
@@ -10658,7 +10658,7 @@
         <v>500</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>10.16</v>
@@ -10670,7 +10670,7 @@
         <v>85</v>
       </c>
       <c r="L210" t="n">
-        <v>42.3</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="211">
@@ -10706,7 +10706,7 @@
         <v>1185</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>1540</v>
+        <v>1304</v>
       </c>
       <c r="I211" s="3" t="n">
         <v>24.43</v>
@@ -10718,7 +10718,7 @@
         <v>87.59999999999999</v>
       </c>
       <c r="L211" t="n">
-        <v>44.4</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="212">
@@ -10754,7 +10754,7 @@
         <v>434</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>564</v>
+        <v>477</v>
       </c>
       <c r="I212" s="3" t="n">
         <v>9.140000000000001</v>
@@ -10766,7 +10766,7 @@
         <v>91.7</v>
       </c>
       <c r="L212" t="n">
-        <v>47.5</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="213">
@@ -10802,7 +10802,7 @@
         <v>233</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="I213" s="3" t="n">
         <v>5.49</v>
@@ -10814,7 +10814,7 @@
         <v>114.6</v>
       </c>
       <c r="L213" t="n">
-        <v>65</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="214">
@@ -10850,7 +10850,7 @@
         <v>448</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>582</v>
+        <v>493</v>
       </c>
       <c r="I214" s="3" t="n">
         <v>11.18</v>
@@ -10862,7 +10862,7 @@
         <v>127</v>
       </c>
       <c r="L214" t="n">
-        <v>74.7</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="215">
@@ -10898,7 +10898,7 @@
         <v>353</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>459</v>
+        <v>388</v>
       </c>
       <c r="I215" s="3" t="n">
         <v>9.140000000000001</v>
@@ -10910,7 +10910,7 @@
         <v>135.7</v>
       </c>
       <c r="L215" t="n">
-        <v>81.3</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="216">
@@ -10946,7 +10946,7 @@
         <v>131</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="I216" s="3" t="n">
         <v>3.51</v>
@@ -10958,7 +10958,7 @@
         <v>143.5</v>
       </c>
       <c r="L216" t="n">
-        <v>87.59999999999999</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="217">
@@ -10994,7 +10994,7 @@
         <v>71</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I217" s="3" t="n">
         <v>2.07</v>
@@ -11006,7 +11006,7 @@
         <v>164.8</v>
       </c>
       <c r="L217" t="n">
-        <v>104.3</v>
+        <v>141</v>
       </c>
     </row>
     <row r="218">
@@ -11042,7 +11042,7 @@
         <v>104</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="I218" s="3" t="n">
         <v>3.05</v>
@@ -11054,7 +11054,7 @@
         <v>167.3</v>
       </c>
       <c r="L218" t="n">
-        <v>105.9</v>
+        <v>143.9</v>
       </c>
     </row>
     <row r="219">
@@ -11090,7 +11090,7 @@
         <v>94</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="I219" s="3" t="n">
         <v>2.83</v>
@@ -11102,7 +11102,7 @@
         <v>174.5</v>
       </c>
       <c r="L219" t="n">
-        <v>111.5</v>
+        <v>150.5</v>
       </c>
     </row>
     <row r="220">
@@ -11138,7 +11138,7 @@
         <v>71</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I220" s="3" t="n">
         <v>2.18</v>
@@ -11150,7 +11150,7 @@
         <v>178.9</v>
       </c>
       <c r="L220" t="n">
-        <v>115.2</v>
+        <v>153.8</v>
       </c>
     </row>
     <row r="221">
@@ -11186,7 +11186,7 @@
         <v>82</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="I221" s="3" t="n">
         <v>2.56</v>
@@ -11198,7 +11198,7 @@
         <v>184.1</v>
       </c>
       <c r="L221" t="n">
-        <v>117.8</v>
+        <v>158.9</v>
       </c>
     </row>
     <row r="222">
@@ -11220,7 +11220,7 @@
         <v>689</v>
       </c>
       <c r="H222" s="5" t="n">
-        <v>895</v>
+        <v>758</v>
       </c>
       <c r="I222" s="6" t="inlineStr"/>
       <c r="J222" s="5" t="n">
@@ -11230,7 +11230,7 @@
         <v>31.4</v>
       </c>
       <c r="L222" s="4" t="n">
-        <v>1</v>
+        <v>19.4</v>
       </c>
     </row>
   </sheetData>
@@ -11330,7 +11330,7 @@
         <v>21.4</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="3">
@@ -11352,7 +11352,7 @@
         <v>41.2</v>
       </c>
       <c r="F3" t="n">
-        <v>8.699999999999999</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="4">
@@ -11374,7 +11374,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>-14.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -11396,7 +11396,7 @@
         <v>12.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-13.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -11418,7 +11418,7 @@
         <v>7.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-17</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="7">
@@ -11440,7 +11440,7 @@
         <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>4.7</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="8">
@@ -11462,7 +11462,7 @@
         <v>34</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="9">
@@ -11484,7 +11484,7 @@
         <v>16.6</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="10">
@@ -11506,7 +11506,7 @@
         <v>38.6</v>
       </c>
       <c r="F10" t="n">
-        <v>6.6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -11528,7 +11528,7 @@
         <v>38.5</v>
       </c>
       <c r="F11" t="n">
-        <v>6.6</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="12">
@@ -11550,7 +11550,7 @@
         <v>31.9</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="13">
@@ -11572,7 +11572,7 @@
         <v>38.8</v>
       </c>
       <c r="F13" t="n">
-        <v>6.8</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="14">
@@ -11594,7 +11594,7 @@
         <v>31.4</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1</v>
+        <v>19.4</v>
       </c>
     </row>
   </sheetData>
@@ -15690,7 +15690,7 @@
         <v>1161</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1509</v>
+        <v>1277</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>11.88</v>
@@ -15702,7 +15702,7 @@
         <v>-6.9</v>
       </c>
       <c r="L2" t="n">
-        <v>-28.4</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="3">
@@ -15738,7 +15738,7 @@
         <v>1843</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2396</v>
+        <v>2027</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>20.74</v>
@@ -15750,7 +15750,7 @@
         <v>2.4</v>
       </c>
       <c r="L3" t="n">
-        <v>-21.2</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="4">
@@ -15786,7 +15786,7 @@
         <v>1110</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1443</v>
+        <v>1221</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>12.53</v>
@@ -15798,7 +15798,7 @@
         <v>2.7</v>
       </c>
       <c r="L4" t="n">
-        <v>-21</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="5">
@@ -15834,7 +15834,7 @@
         <v>1918</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2493</v>
+        <v>2110</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>22.03</v>
@@ -15846,7 +15846,7 @@
         <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-19.6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="6">
@@ -15882,7 +15882,7 @@
         <v>1257</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1634</v>
+        <v>1383</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>14.69</v>
@@ -15894,7 +15894,7 @@
         <v>6.4</v>
       </c>
       <c r="L6" t="n">
-        <v>-18.2</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="7">
@@ -15930,7 +15930,7 @@
         <v>1128</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1466</v>
+        <v>1241</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>13.39</v>
@@ -15942,7 +15942,7 @@
         <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>-16.9</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="8">
@@ -15978,7 +15978,7 @@
         <v>832</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1082</v>
+        <v>915</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>9.94</v>
@@ -15990,7 +15990,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-16.4</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="9">
@@ -16026,7 +16026,7 @@
         <v>1257</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1634</v>
+        <v>1383</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>15.12</v>
@@ -16038,7 +16038,7 @@
         <v>9.5</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.8</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="10">
@@ -16074,7 +16074,7 @@
         <v>808</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1050</v>
+        <v>889</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>9.720000000000001</v>
@@ -16086,7 +16086,7 @@
         <v>9.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.7</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="11">
@@ -16122,7 +16122,7 @@
         <v>839</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1091</v>
+        <v>923</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>10.15</v>
@@ -16134,7 +16134,7 @@
         <v>10.1</v>
       </c>
       <c r="L11" t="n">
-        <v>-15.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -16170,7 +16170,7 @@
         <v>837</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1088</v>
+        <v>921</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>10.15</v>
@@ -16182,7 +16182,7 @@
         <v>10.4</v>
       </c>
       <c r="L12" t="n">
-        <v>-15.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -16218,7 +16218,7 @@
         <v>965</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1254</v>
+        <v>1062</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>11.88</v>
@@ -16230,7 +16230,7 @@
         <v>12</v>
       </c>
       <c r="L13" t="n">
-        <v>-13.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14">
@@ -16266,7 +16266,7 @@
         <v>1128</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1466</v>
+        <v>1241</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>14.04</v>
@@ -16278,7 +16278,7 @@
         <v>13.3</v>
       </c>
       <c r="L14" t="n">
-        <v>-12.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -16314,7 +16314,7 @@
         <v>771</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1002</v>
+        <v>848</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>9.720000000000001</v>
@@ -16326,7 +16326,7 @@
         <v>14.8</v>
       </c>
       <c r="L15" t="n">
-        <v>-11.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="16">
@@ -16362,7 +16362,7 @@
         <v>837</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1088</v>
+        <v>921</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>10.59</v>
@@ -16374,7 +16374,7 @@
         <v>15.2</v>
       </c>
       <c r="L16" t="n">
-        <v>-11.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="17">
@@ -16410,7 +16410,7 @@
         <v>851</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1106</v>
+        <v>936</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>10.8</v>
@@ -16422,7 +16422,7 @@
         <v>15.5</v>
       </c>
       <c r="L17" t="n">
-        <v>-11.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -16458,7 +16458,7 @@
         <v>935</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1216</v>
+        <v>1028</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>11.88</v>
@@ -16470,7 +16470,7 @@
         <v>15.6</v>
       </c>
       <c r="L18" t="n">
-        <v>-11.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="19">
@@ -16506,7 +16506,7 @@
         <v>725</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>942</v>
+        <v>798</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>9.289999999999999</v>
@@ -16518,7 +16518,7 @@
         <v>16.6</v>
       </c>
       <c r="L19" t="n">
-        <v>-10.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="20">
@@ -16554,7 +16554,7 @@
         <v>747</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>971</v>
+        <v>822</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>9.720000000000001</v>
@@ -16566,7 +16566,7 @@
         <v>18.5</v>
       </c>
       <c r="L20" t="n">
-        <v>-8.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="21">
@@ -16602,7 +16602,7 @@
         <v>677</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>880</v>
+        <v>745</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>8.859999999999999</v>
@@ -16614,7 +16614,7 @@
         <v>19.1</v>
       </c>
       <c r="L21" t="n">
-        <v>-8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -16650,7 +16650,7 @@
         <v>758</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>985</v>
+        <v>834</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>9.94</v>
@@ -16662,7 +16662,7 @@
         <v>19.4</v>
       </c>
       <c r="L22" t="n">
-        <v>-8.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="23">
@@ -16698,7 +16698,7 @@
         <v>1019</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1325</v>
+        <v>1121</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>13.39</v>
@@ -16710,7 +16710,7 @@
         <v>19.5</v>
       </c>
       <c r="L23" t="n">
-        <v>-8.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -16746,7 +16746,7 @@
         <v>1032</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1342</v>
+        <v>1135</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>13.61</v>
@@ -16758,7 +16758,7 @@
         <v>20.1</v>
       </c>
       <c r="L24" t="n">
-        <v>-7.7</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -16794,7 +16794,7 @@
         <v>1032</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1342</v>
+        <v>1135</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>13.61</v>
@@ -16806,7 +16806,7 @@
         <v>20.1</v>
       </c>
       <c r="L25" t="n">
-        <v>-7.7</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -16842,7 +16842,7 @@
         <v>818</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1063</v>
+        <v>900</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>10.8</v>
@@ -16854,7 +16854,7 @@
         <v>20.2</v>
       </c>
       <c r="L26" t="n">
-        <v>-7.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -16890,7 +16890,7 @@
         <v>652</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>848</v>
+        <v>717</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>8.640000000000001</v>
@@ -16902,7 +16902,7 @@
         <v>20.6</v>
       </c>
       <c r="L27" t="n">
-        <v>-7.3</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="28">
@@ -16938,7 +16938,7 @@
         <v>1054</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1370</v>
+        <v>1159</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>14.04</v>
@@ -16950,7 +16950,7 @@
         <v>21.3</v>
       </c>
       <c r="L28" t="n">
-        <v>-6.7</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="29">
@@ -16986,7 +16986,7 @@
         <v>921</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1197</v>
+        <v>1013</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>12.31</v>
@@ -16998,7 +16998,7 @@
         <v>21.6</v>
       </c>
       <c r="L29" t="n">
-        <v>-6.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="30">
@@ -17034,7 +17034,7 @@
         <v>725</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>942</v>
+        <v>798</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>9.720000000000001</v>
@@ -17046,7 +17046,7 @@
         <v>22.1</v>
       </c>
       <c r="L30" t="n">
-        <v>-6.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="31">
@@ -17082,7 +17082,7 @@
         <v>719</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>935</v>
+        <v>791</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>9.720000000000001</v>
@@ -17094,7 +17094,7 @@
         <v>23.1</v>
       </c>
       <c r="L31" t="n">
-        <v>-5.3</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="32">
@@ -17130,7 +17130,7 @@
         <v>638</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>829</v>
+        <v>702</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>8.640000000000001</v>
@@ -17142,7 +17142,7 @@
         <v>23.2</v>
       </c>
       <c r="L32" t="n">
-        <v>-5.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -17178,7 +17178,7 @@
         <v>905</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>1176</v>
+        <v>996</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>12.31</v>
@@ -17190,7 +17190,7 @@
         <v>23.8</v>
       </c>
       <c r="L33" t="n">
-        <v>-4.8</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="34">
@@ -17226,7 +17226,7 @@
         <v>841</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1093</v>
+        <v>925</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>11.45</v>
@@ -17238,7 +17238,7 @@
         <v>23.9</v>
       </c>
       <c r="L34" t="n">
-        <v>-4.7</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="35">
@@ -17274,7 +17274,7 @@
         <v>697</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>906</v>
+        <v>767</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>9.51</v>
@@ -17286,7 +17286,7 @@
         <v>24.1</v>
       </c>
       <c r="L35" t="n">
-        <v>-4.5</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="36">
@@ -17322,7 +17322,7 @@
         <v>712</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>926</v>
+        <v>783</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>9.720000000000001</v>
@@ -17334,7 +17334,7 @@
         <v>24.3</v>
       </c>
       <c r="L36" t="n">
-        <v>-4.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
@@ -17370,7 +17370,7 @@
         <v>712</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>926</v>
+        <v>783</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>9.720000000000001</v>
@@ -17382,7 +17382,7 @@
         <v>24.3</v>
       </c>
       <c r="L37" t="n">
-        <v>-4.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
@@ -17418,7 +17418,7 @@
         <v>993</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1291</v>
+        <v>1092</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>13.61</v>
@@ -17430,7 +17430,7 @@
         <v>24.8</v>
       </c>
       <c r="L38" t="n">
-        <v>-4</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="39">
@@ -17466,7 +17466,7 @@
         <v>1228</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1596</v>
+        <v>1351</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>16.85</v>
@@ -17478,7 +17478,7 @@
         <v>24.8</v>
       </c>
       <c r="L39" t="n">
-        <v>-3.9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="40">
@@ -17514,7 +17514,7 @@
         <v>740</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>962</v>
+        <v>814</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>10.15</v>
@@ -17526,7 +17526,7 @@
         <v>24.9</v>
       </c>
       <c r="L40" t="n">
-        <v>-4</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="41">
@@ -17562,7 +17562,7 @@
         <v>706</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>918</v>
+        <v>777</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>9.720000000000001</v>
@@ -17574,7 +17574,7 @@
         <v>25.4</v>
       </c>
       <c r="L41" t="n">
-        <v>-3.6</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="42">
@@ -17610,7 +17610,7 @@
         <v>690</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>897</v>
+        <v>759</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>9.51</v>
@@ -17622,7 +17622,7 @@
         <v>25.4</v>
       </c>
       <c r="L42" t="n">
-        <v>-3.6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
@@ -17658,7 +17658,7 @@
         <v>1002</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1303</v>
+        <v>1102</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>13.83</v>
@@ -17670,7 +17670,7 @@
         <v>25.6</v>
       </c>
       <c r="L43" t="n">
-        <v>-3.4</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="44">
@@ -17706,7 +17706,7 @@
         <v>688</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>894</v>
+        <v>757</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>9.51</v>
@@ -17718,7 +17718,7 @@
         <v>25.7</v>
       </c>
       <c r="L44" t="n">
-        <v>-3.2</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="45">
@@ -17754,7 +17754,7 @@
         <v>795</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1034</v>
+        <v>875</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>11.02</v>
@@ -17766,7 +17766,7 @@
         <v>26.2</v>
       </c>
       <c r="L45" t="n">
-        <v>-3</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="46">
@@ -17802,7 +17802,7 @@
         <v>589</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>766</v>
+        <v>648</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>8.210000000000001</v>
@@ -17814,7 +17814,7 @@
         <v>26.8</v>
       </c>
       <c r="L46" t="n">
-        <v>-2.5</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="47">
@@ -17850,7 +17850,7 @@
         <v>1161</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>1509</v>
+        <v>1277</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>16.2</v>
@@ -17862,7 +17862,7 @@
         <v>27</v>
       </c>
       <c r="L47" t="n">
-        <v>-2.3</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="48">
@@ -17898,7 +17898,7 @@
         <v>774</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1006</v>
+        <v>851</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>10.8</v>
@@ -17910,7 +17910,7 @@
         <v>27</v>
       </c>
       <c r="L48" t="n">
-        <v>-2.3</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="49">
@@ -17946,7 +17946,7 @@
         <v>774</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1006</v>
+        <v>851</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>10.8</v>
@@ -17958,7 +17958,7 @@
         <v>27</v>
       </c>
       <c r="L49" t="n">
-        <v>-2.3</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="50">
@@ -17994,7 +17994,7 @@
         <v>896</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>1165</v>
+        <v>986</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>12.53</v>
@@ -18006,7 +18006,7 @@
         <v>27.2</v>
       </c>
       <c r="L50" t="n">
-        <v>-2.1</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="51">
@@ -18042,7 +18042,7 @@
         <v>725</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>942</v>
+        <v>798</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>10.15</v>
@@ -18054,7 +18054,7 @@
         <v>27.4</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.9</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="52">
@@ -18090,7 +18090,7 @@
         <v>694</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>902</v>
+        <v>763</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>9.720000000000001</v>
@@ -18102,7 +18102,7 @@
         <v>27.5</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
@@ -18138,7 +18138,7 @@
         <v>693</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>901</v>
+        <v>762</v>
       </c>
       <c r="I53" s="3" t="n">
         <v>9.720000000000001</v>
@@ -18150,7 +18150,7 @@
         <v>27.7</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.8</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="54">
@@ -18186,7 +18186,7 @@
         <v>739</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>961</v>
+        <v>813</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>10.37</v>
@@ -18198,7 +18198,7 @@
         <v>27.7</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.8</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="55">
@@ -18234,7 +18234,7 @@
         <v>693</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>901</v>
+        <v>762</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>9.720000000000001</v>
@@ -18246,7 +18246,7 @@
         <v>27.7</v>
       </c>
       <c r="L55" t="n">
-        <v>-1.8</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="56">
@@ -18282,7 +18282,7 @@
         <v>846</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1100</v>
+        <v>931</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>11.88</v>
@@ -18294,7 +18294,7 @@
         <v>27.8</v>
       </c>
       <c r="L56" t="n">
-        <v>-1.7</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="57">
@@ -18330,7 +18330,7 @@
         <v>614</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>798</v>
+        <v>675</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>8.640000000000001</v>
@@ -18342,7 +18342,7 @@
         <v>28</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.5</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="58">
@@ -18378,7 +18378,7 @@
         <v>614</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>798</v>
+        <v>675</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>8.640000000000001</v>
@@ -18390,7 +18390,7 @@
         <v>28</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.5</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="59">
@@ -18426,7 +18426,7 @@
         <v>564</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>733</v>
+        <v>620</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>7.99</v>
@@ -18438,7 +18438,7 @@
         <v>28.9</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.8</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="60">
@@ -18474,7 +18474,7 @@
         <v>1036</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1347</v>
+        <v>1140</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>14.69</v>
@@ -18486,7 +18486,7 @@
         <v>29.1</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.7</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="61">
@@ -18522,7 +18522,7 @@
         <v>741</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>963</v>
+        <v>815</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>10.59</v>
@@ -18534,7 +18534,7 @@
         <v>30.1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.1</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="62">
@@ -18570,7 +18570,7 @@
         <v>709</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>922</v>
+        <v>780</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>10.15</v>
@@ -18582,7 +18582,7 @@
         <v>30.3</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="63">
@@ -18618,7 +18618,7 @@
         <v>603</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>784</v>
+        <v>663</v>
       </c>
       <c r="I63" s="3" t="n">
         <v>8.640000000000001</v>
@@ -18630,7 +18630,7 @@
         <v>30.3</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="64">
@@ -18666,7 +18666,7 @@
         <v>903</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1174</v>
+        <v>993</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>12.96</v>
@@ -18678,7 +18678,7 @@
         <v>30.6</v>
       </c>
       <c r="L64" t="n">
-        <v>0.4</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="65">
@@ -18714,7 +18714,7 @@
         <v>674</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>876</v>
+        <v>741</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>9.720000000000001</v>
@@ -18726,7 +18726,7 @@
         <v>31.3</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="66">
@@ -18762,7 +18762,7 @@
         <v>674</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>876</v>
+        <v>741</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>9.720000000000001</v>
@@ -18774,7 +18774,7 @@
         <v>31.3</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="67">
@@ -18810,7 +18810,7 @@
         <v>821</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1067</v>
+        <v>903</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>11.88</v>
@@ -18822,7 +18822,7 @@
         <v>31.7</v>
       </c>
       <c r="L67" t="n">
-        <v>1.3</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="68">
@@ -18858,7 +18858,7 @@
         <v>774</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>1006</v>
+        <v>851</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>11.23</v>
@@ -18870,7 +18870,7 @@
         <v>32</v>
       </c>
       <c r="L68" t="n">
-        <v>1.6</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="69">
@@ -18906,7 +18906,7 @@
         <v>669</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>870</v>
+        <v>736</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>9.720000000000001</v>
@@ -18918,7 +18918,7 @@
         <v>32.3</v>
       </c>
       <c r="L69" t="n">
-        <v>1.7</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="70">
@@ -18954,7 +18954,7 @@
         <v>446</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>580</v>
+        <v>491</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>6.48</v>
@@ -18966,7 +18966,7 @@
         <v>32.3</v>
       </c>
       <c r="L70" t="n">
-        <v>1.7</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="71">
@@ -19002,7 +19002,7 @@
         <v>739</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>961</v>
+        <v>813</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>10.8</v>
@@ -19014,7 +19014,7 @@
         <v>33</v>
       </c>
       <c r="L71" t="n">
-        <v>2.3</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="72">
@@ -19050,7 +19050,7 @@
         <v>694</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>902</v>
+        <v>763</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>10.15</v>
@@ -19062,7 +19062,7 @@
         <v>33.1</v>
       </c>
       <c r="L72" t="n">
-        <v>2.4</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="73">
@@ -19098,7 +19098,7 @@
         <v>620</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>806</v>
+        <v>682</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>9.07</v>
@@ -19110,7 +19110,7 @@
         <v>33.1</v>
       </c>
       <c r="L73" t="n">
-        <v>2.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
@@ -19146,7 +19146,7 @@
         <v>806</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>1048</v>
+        <v>887</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>11.88</v>
@@ -19158,7 +19158,7 @@
         <v>34.1</v>
       </c>
       <c r="L74" t="n">
-        <v>3.1</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="75">
@@ -19194,7 +19194,7 @@
         <v>508</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>660</v>
+        <v>559</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>7.56</v>
@@ -19206,7 +19206,7 @@
         <v>35.4</v>
       </c>
       <c r="L75" t="n">
-        <v>4.2</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="76">
@@ -19242,7 +19242,7 @@
         <v>623</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>810</v>
+        <v>685</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>9.289999999999999</v>
@@ -19254,7 +19254,7 @@
         <v>35.6</v>
       </c>
       <c r="L76" t="n">
-        <v>4.3</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="77">
@@ -19290,7 +19290,7 @@
         <v>721</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>937</v>
+        <v>793</v>
       </c>
       <c r="I77" s="3" t="n">
         <v>10.8</v>
@@ -19302,7 +19302,7 @@
         <v>36.3</v>
       </c>
       <c r="L77" t="n">
-        <v>4.9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
@@ -19338,7 +19338,7 @@
         <v>676</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>879</v>
+        <v>744</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>10.15</v>
@@ -19350,7 +19350,7 @@
         <v>36.7</v>
       </c>
       <c r="L78" t="n">
-        <v>5.1</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="79">
@@ -19386,7 +19386,7 @@
         <v>529</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>688</v>
+        <v>582</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>7.99</v>
@@ -19398,7 +19398,7 @@
         <v>37.4</v>
       </c>
       <c r="L79" t="n">
-        <v>5.7</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="80">
@@ -19434,7 +19434,7 @@
         <v>614</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>798</v>
+        <v>675</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>9.289999999999999</v>
@@ -19446,7 +19446,7 @@
         <v>37.6</v>
       </c>
       <c r="L80" t="n">
-        <v>5.9</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="81">
@@ -19482,7 +19482,7 @@
         <v>614</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>798</v>
+        <v>675</v>
       </c>
       <c r="I81" s="3" t="n">
         <v>9.289999999999999</v>
@@ -19494,7 +19494,7 @@
         <v>37.6</v>
       </c>
       <c r="L81" t="n">
-        <v>5.9</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="82">
@@ -19530,7 +19530,7 @@
         <v>709</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>922</v>
+        <v>780</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>10.8</v>
@@ -19542,7 +19542,7 @@
         <v>38.6</v>
       </c>
       <c r="L82" t="n">
-        <v>6.6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
@@ -19578,7 +19578,7 @@
         <v>822</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>1069</v>
+        <v>904</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>12.53</v>
@@ -19590,7 +19590,7 @@
         <v>38.7</v>
       </c>
       <c r="L83" t="n">
-        <v>6.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="84">
@@ -19626,7 +19626,7 @@
         <v>822</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1069</v>
+        <v>904</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>12.53</v>
@@ -19638,7 +19638,7 @@
         <v>38.7</v>
       </c>
       <c r="L84" t="n">
-        <v>6.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="85">
@@ -19674,7 +19674,7 @@
         <v>822</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>1069</v>
+        <v>904</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>12.53</v>
@@ -19686,7 +19686,7 @@
         <v>38.7</v>
       </c>
       <c r="L85" t="n">
-        <v>6.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="86">
@@ -19722,7 +19722,7 @@
         <v>635</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>826</v>
+        <v>698</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>9.720000000000001</v>
@@ -19734,7 +19734,7 @@
         <v>39.4</v>
       </c>
       <c r="L86" t="n">
-        <v>7.1</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="87">
@@ -19770,7 +19770,7 @@
         <v>873</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>1135</v>
+        <v>960</v>
       </c>
       <c r="I87" s="3" t="n">
         <v>13.39</v>
@@ -19782,7 +19782,7 @@
         <v>39.5</v>
       </c>
       <c r="L87" t="n">
-        <v>7.3</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="88">
@@ -19818,7 +19818,7 @@
         <v>774</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>1006</v>
+        <v>851</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>11.88</v>
@@ -19830,7 +19830,7 @@
         <v>39.7</v>
       </c>
       <c r="L88" t="n">
-        <v>7.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
@@ -19866,7 +19866,7 @@
         <v>745</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>968</v>
+        <v>820</v>
       </c>
       <c r="I89" s="3" t="n">
         <v>11.45</v>
@@ -19878,7 +19878,7 @@
         <v>39.9</v>
       </c>
       <c r="L89" t="n">
-        <v>7.6</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="90">
@@ -19914,7 +19914,7 @@
         <v>870</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>1131</v>
+        <v>957</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>13.39</v>
@@ -19926,7 +19926,7 @@
         <v>40</v>
       </c>
       <c r="L90" t="n">
-        <v>7.7</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="91">
@@ -19962,7 +19962,7 @@
         <v>729</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>948</v>
+        <v>802</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>11.23</v>
@@ -19974,7 +19974,7 @@
         <v>40.2</v>
       </c>
       <c r="L91" t="n">
-        <v>7.8</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="92">
@@ -20010,7 +20010,7 @@
         <v>631</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>820</v>
+        <v>694</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>9.720000000000001</v>
@@ -20022,7 +20022,7 @@
         <v>40.3</v>
       </c>
       <c r="L92" t="n">
-        <v>7.9</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="93">
@@ -20058,7 +20058,7 @@
         <v>770</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>1001</v>
+        <v>847</v>
       </c>
       <c r="I93" s="3" t="n">
         <v>11.88</v>
@@ -20070,7 +20070,7 @@
         <v>40.4</v>
       </c>
       <c r="L93" t="n">
-        <v>8</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="94">
@@ -20106,7 +20106,7 @@
         <v>806</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>1048</v>
+        <v>887</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>12.53</v>
@@ -20118,7 +20118,7 @@
         <v>41.4</v>
       </c>
       <c r="L94" t="n">
-        <v>8.800000000000001</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="95">
@@ -20154,7 +20154,7 @@
         <v>555</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>722</v>
+        <v>610</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>8.640000000000001</v>
@@ -20166,7 +20166,7 @@
         <v>41.6</v>
       </c>
       <c r="L95" t="n">
-        <v>8.9</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="96">
@@ -20202,7 +20202,7 @@
         <v>596</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>775</v>
+        <v>656</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>9.289999999999999</v>
@@ -20214,7 +20214,7 @@
         <v>41.8</v>
       </c>
       <c r="L96" t="n">
-        <v>9</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="97">
@@ -20250,7 +20250,7 @@
         <v>664</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>863</v>
+        <v>730</v>
       </c>
       <c r="I97" s="3" t="n">
         <v>10.37</v>
@@ -20262,7 +20262,7 @@
         <v>42.2</v>
       </c>
       <c r="L97" t="n">
-        <v>9.4</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="98">
@@ -20298,7 +20298,7 @@
         <v>592</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>770</v>
+        <v>651</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>9.289999999999999</v>
@@ -20310,7 +20310,7 @@
         <v>42.7</v>
       </c>
       <c r="L98" t="n">
-        <v>9.699999999999999</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="99">
@@ -20346,7 +20346,7 @@
         <v>620</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>806</v>
+        <v>682</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>9.720000000000001</v>
@@ -20358,7 +20358,7 @@
         <v>42.7</v>
       </c>
       <c r="L99" t="n">
-        <v>9.800000000000001</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="100">
@@ -20394,7 +20394,7 @@
         <v>825</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>1072</v>
+        <v>908</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>12.96</v>
@@ -20406,7 +20406,7 @@
         <v>42.9</v>
       </c>
       <c r="L100" t="n">
-        <v>10</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="101">
@@ -20442,7 +20442,7 @@
         <v>603</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>784</v>
+        <v>663</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>9.51</v>
@@ -20454,7 +20454,7 @@
         <v>43.4</v>
       </c>
       <c r="L101" t="n">
-        <v>10.3</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="102">
@@ -20490,7 +20490,7 @@
         <v>548</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>712</v>
+        <v>603</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>8.640000000000001</v>
@@ -20502,7 +20502,7 @@
         <v>43.4</v>
       </c>
       <c r="L102" t="n">
-        <v>10.4</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="103">
@@ -20538,7 +20538,7 @@
         <v>479</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>623</v>
+        <v>527</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>7.56</v>
@@ -20550,7 +20550,7 @@
         <v>43.6</v>
       </c>
       <c r="L103" t="n">
-        <v>10.4</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="104">
@@ -20586,7 +20586,7 @@
         <v>614</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>798</v>
+        <v>675</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>9.720000000000001</v>
@@ -20598,7 +20598,7 @@
         <v>44.1</v>
       </c>
       <c r="L104" t="n">
-        <v>10.9</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="105">
@@ -20634,7 +20634,7 @@
         <v>531</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>690</v>
+        <v>584</v>
       </c>
       <c r="I105" s="3" t="n">
         <v>8.43</v>
@@ -20646,7 +20646,7 @@
         <v>44.4</v>
       </c>
       <c r="L105" t="n">
-        <v>11.2</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="106">
@@ -20682,7 +20682,7 @@
         <v>544</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>707</v>
+        <v>598</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>8.640000000000001</v>
@@ -20694,7 +20694,7 @@
         <v>44.5</v>
       </c>
       <c r="L106" t="n">
-        <v>11.2</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="107">
@@ -20730,7 +20730,7 @@
         <v>774</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>1006</v>
+        <v>851</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>12.31</v>
@@ -20742,7 +20742,7 @@
         <v>44.7</v>
       </c>
       <c r="L107" t="n">
-        <v>11.3</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="108">
@@ -20778,7 +20778,7 @@
         <v>757</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>984</v>
+        <v>833</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>12.1</v>
@@ -20790,7 +20790,7 @@
         <v>45.4</v>
       </c>
       <c r="L108" t="n">
-        <v>11.9</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="109">
@@ -20826,7 +20826,7 @@
         <v>607</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>789</v>
+        <v>668</v>
       </c>
       <c r="I109" s="3" t="n">
         <v>9.720000000000001</v>
@@ -20838,7 +20838,7 @@
         <v>45.8</v>
       </c>
       <c r="L109" t="n">
-        <v>12.2</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="110">
@@ -20874,7 +20874,7 @@
         <v>781</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>1015</v>
+        <v>859</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>12.53</v>
@@ -20886,7 +20886,7 @@
         <v>46</v>
       </c>
       <c r="L110" t="n">
-        <v>12.3</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="111">
@@ -20922,7 +20922,7 @@
         <v>525</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>682</v>
+        <v>578</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>8.43</v>
@@ -20934,7 +20934,7 @@
         <v>46.1</v>
       </c>
       <c r="L111" t="n">
-        <v>12.5</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="112">
@@ -20970,7 +20970,7 @@
         <v>1008</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>1310</v>
+        <v>1109</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>16.2</v>
@@ -20982,7 +20982,7 @@
         <v>46.2</v>
       </c>
       <c r="L112" t="n">
-        <v>12.5</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="113">
@@ -21018,7 +21018,7 @@
         <v>521</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>677</v>
+        <v>573</v>
       </c>
       <c r="I113" s="3" t="n">
         <v>8.43</v>
@@ -21030,7 +21030,7 @@
         <v>47.2</v>
       </c>
       <c r="L113" t="n">
-        <v>13.3</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="114">
@@ -21066,7 +21066,7 @@
         <v>868</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>1128</v>
+        <v>955</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>14.04</v>
@@ -21078,7 +21078,7 @@
         <v>47.2</v>
       </c>
       <c r="L114" t="n">
-        <v>13.3</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="115">
@@ -21114,7 +21114,7 @@
         <v>467</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>607</v>
+        <v>514</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>7.56</v>
@@ -21126,7 +21126,7 @@
         <v>47.3</v>
       </c>
       <c r="L115" t="n">
-        <v>13.3</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="116">
@@ -21162,7 +21162,7 @@
         <v>600</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>780</v>
+        <v>660</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>9.720000000000001</v>
@@ -21174,7 +21174,7 @@
         <v>47.5</v>
       </c>
       <c r="L116" t="n">
-        <v>13.5</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="117">
@@ -21210,7 +21210,7 @@
         <v>613</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>797</v>
+        <v>674</v>
       </c>
       <c r="I117" s="3" t="n">
         <v>9.94</v>
@@ -21222,7 +21222,7 @@
         <v>47.6</v>
       </c>
       <c r="L117" t="n">
-        <v>13.6</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="118">
@@ -21258,7 +21258,7 @@
         <v>597</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>776</v>
+        <v>657</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>9.720000000000001</v>
@@ -21270,7 +21270,7 @@
         <v>48.2</v>
       </c>
       <c r="L118" t="n">
-        <v>14</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="119">
@@ -21306,7 +21306,7 @@
         <v>729</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>948</v>
+        <v>802</v>
       </c>
       <c r="I119" s="3" t="n">
         <v>11.88</v>
@@ -21318,7 +21318,7 @@
         <v>48.3</v>
       </c>
       <c r="L119" t="n">
-        <v>14</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="120">
@@ -21354,7 +21354,7 @@
         <v>856</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>1113</v>
+        <v>942</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>14.04</v>
@@ -21366,7 +21366,7 @@
         <v>49.3</v>
       </c>
       <c r="L120" t="n">
-        <v>14.8</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="121">
@@ -21402,7 +21402,7 @@
         <v>540</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>702</v>
+        <v>594</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>8.859999999999999</v>
@@ -21414,7 +21414,7 @@
         <v>49.3</v>
       </c>
       <c r="L121" t="n">
-        <v>14.8</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="122">
@@ -21450,7 +21450,7 @@
         <v>469</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>610</v>
+        <v>516</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>7.78</v>
@@ -21462,7 +21462,7 @@
         <v>51</v>
       </c>
       <c r="L122" t="n">
-        <v>16.1</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="123">
@@ -21498,7 +21498,7 @@
         <v>806</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>1048</v>
+        <v>887</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>13.39</v>
@@ -21510,7 +21510,7 @@
         <v>51.1</v>
       </c>
       <c r="L123" t="n">
-        <v>16.2</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="124">
@@ -21546,7 +21546,7 @@
         <v>493</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>641</v>
+        <v>542</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>8.210000000000001</v>
@@ -21558,7 +21558,7 @@
         <v>51.5</v>
       </c>
       <c r="L124" t="n">
-        <v>16.5</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="125">
@@ -21594,7 +21594,7 @@
         <v>479</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>623</v>
+        <v>527</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>7.99</v>
@@ -21606,7 +21606,7 @@
         <v>51.8</v>
       </c>
       <c r="L125" t="n">
-        <v>16.7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="126">
@@ -21642,7 +21642,7 @@
         <v>672</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>874</v>
+        <v>739</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>11.23</v>
@@ -21654,7 +21654,7 @@
         <v>52.1</v>
       </c>
       <c r="L126" t="n">
-        <v>16.9</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="127">
@@ -21690,7 +21690,7 @@
         <v>709</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>922</v>
+        <v>780</v>
       </c>
       <c r="I127" s="3" t="n">
         <v>11.88</v>
@@ -21702,7 +21702,7 @@
         <v>52.5</v>
       </c>
       <c r="L127" t="n">
-        <v>17.2</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="128">
@@ -21738,7 +21738,7 @@
         <v>705</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>916</v>
+        <v>776</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>11.88</v>
@@ -21750,7 +21750,7 @@
         <v>53.3</v>
       </c>
       <c r="L128" t="n">
-        <v>18</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="129">
@@ -21786,7 +21786,7 @@
         <v>558</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>725</v>
+        <v>614</v>
       </c>
       <c r="I129" s="3" t="n">
         <v>9.51</v>
@@ -21798,7 +21798,7 @@
         <v>55</v>
       </c>
       <c r="L129" t="n">
-        <v>19.3</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="130">
@@ -21834,7 +21834,7 @@
         <v>922</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>1199</v>
+        <v>1014</v>
       </c>
       <c r="I130" s="3" t="n">
         <v>15.77</v>
@@ -21846,7 +21846,7 @@
         <v>55.6</v>
       </c>
       <c r="L130" t="n">
-        <v>19.7</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="131">
@@ -21882,7 +21882,7 @@
         <v>567</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>737</v>
+        <v>624</v>
       </c>
       <c r="I131" s="3" t="n">
         <v>9.720000000000001</v>
@@ -21894,7 +21894,7 @@
         <v>56.1</v>
       </c>
       <c r="L131" t="n">
-        <v>20.1</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="132">
@@ -21930,7 +21930,7 @@
         <v>501</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>651</v>
+        <v>551</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>8.640000000000001</v>
@@ -21942,7 +21942,7 @@
         <v>56.9</v>
       </c>
       <c r="L132" t="n">
-        <v>20.7</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="133">
@@ -21978,7 +21978,7 @@
         <v>622</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>809</v>
+        <v>684</v>
       </c>
       <c r="I133" s="3" t="n">
         <v>10.8</v>
@@ -21990,7 +21990,7 @@
         <v>58</v>
       </c>
       <c r="L133" t="n">
-        <v>21.5</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="134">
@@ -22026,7 +22026,7 @@
         <v>733</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>953</v>
+        <v>806</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>12.75</v>
@@ -22038,7 +22038,7 @@
         <v>58.3</v>
       </c>
       <c r="L134" t="n">
-        <v>21.7</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="135">
@@ -22074,7 +22074,7 @@
         <v>645</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>838</v>
+        <v>710</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>11.23</v>
@@ -22086,7 +22086,7 @@
         <v>58.4</v>
       </c>
       <c r="L135" t="n">
-        <v>22</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="136">
@@ -22122,7 +22122,7 @@
         <v>335</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>436</v>
+        <v>369</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>5.83</v>
@@ -22134,7 +22134,7 @@
         <v>58.5</v>
       </c>
       <c r="L136" t="n">
-        <v>21.8</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="137">
@@ -22170,7 +22170,7 @@
         <v>657</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>854</v>
+        <v>723</v>
       </c>
       <c r="I137" s="3" t="n">
         <v>11.45</v>
@@ -22182,7 +22182,7 @@
         <v>58.6</v>
       </c>
       <c r="L137" t="n">
-        <v>22</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="138">
@@ -22218,7 +22218,7 @@
         <v>458</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>595</v>
+        <v>504</v>
       </c>
       <c r="I138" s="3" t="n">
         <v>7.99</v>
@@ -22230,7 +22230,7 @@
         <v>58.7</v>
       </c>
       <c r="L138" t="n">
-        <v>22.2</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="139">
@@ -22266,7 +22266,7 @@
         <v>557</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>724</v>
+        <v>613</v>
       </c>
       <c r="I139" s="3" t="n">
         <v>9.720000000000001</v>
@@ -22278,7 +22278,7 @@
         <v>58.9</v>
       </c>
       <c r="L139" t="n">
-        <v>22.2</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="140">
@@ -22314,7 +22314,7 @@
         <v>333</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>433</v>
+        <v>366</v>
       </c>
       <c r="I140" s="3" t="n">
         <v>5.83</v>
@@ -22326,7 +22326,7 @@
         <v>59.5</v>
       </c>
       <c r="L140" t="n">
-        <v>22.6</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="141">
@@ -22362,7 +22362,7 @@
         <v>674</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>876</v>
+        <v>741</v>
       </c>
       <c r="I141" s="3" t="n">
         <v>11.88</v>
@@ -22374,7 +22374,7 @@
         <v>60.4</v>
       </c>
       <c r="L141" t="n">
-        <v>23.4</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="142">
@@ -22410,7 +22410,7 @@
         <v>558</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>725</v>
+        <v>614</v>
       </c>
       <c r="I142" s="3" t="n">
         <v>9.94</v>
@@ -22422,7 +22422,7 @@
         <v>62.2</v>
       </c>
       <c r="L142" t="n">
-        <v>24.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="143">
@@ -22458,7 +22458,7 @@
         <v>821</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>1067</v>
+        <v>903</v>
       </c>
       <c r="I143" s="3" t="n">
         <v>14.69</v>
@@ -22470,7 +22470,7 @@
         <v>62.9</v>
       </c>
       <c r="L143" t="n">
-        <v>25.3</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="144">
@@ -22506,7 +22506,7 @@
         <v>502</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>653</v>
+        <v>552</v>
       </c>
       <c r="I144" s="3" t="n">
         <v>9.07</v>
@@ -22518,7 +22518,7 @@
         <v>64.3</v>
       </c>
       <c r="L144" t="n">
-        <v>26.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="145">
@@ -22554,7 +22554,7 @@
         <v>694</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>902</v>
+        <v>763</v>
       </c>
       <c r="I145" s="3" t="n">
         <v>12.53</v>
@@ -22566,7 +22566,7 @@
         <v>64.3</v>
       </c>
       <c r="L145" t="n">
-        <v>26.4</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="146">
@@ -22602,7 +22602,7 @@
         <v>585</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>760</v>
+        <v>644</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>10.59</v>
@@ -22614,7 +22614,7 @@
         <v>64.8</v>
       </c>
       <c r="L146" t="n">
-        <v>26.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="147">
@@ -22650,7 +22650,7 @@
         <v>564</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>733</v>
+        <v>620</v>
       </c>
       <c r="I147" s="3" t="n">
         <v>10.37</v>
@@ -22662,7 +22662,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="L147" t="n">
-        <v>28.8</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="148">
@@ -22698,7 +22698,7 @@
         <v>446</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>580</v>
+        <v>491</v>
       </c>
       <c r="I148" s="3" t="n">
         <v>8.210000000000001</v>
@@ -22710,7 +22710,7 @@
         <v>67.5</v>
       </c>
       <c r="L148" t="n">
-        <v>28.8</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="149">
@@ -22746,7 +22746,7 @@
         <v>433</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>563</v>
+        <v>476</v>
       </c>
       <c r="I149" s="3" t="n">
         <v>7.99</v>
@@ -22758,7 +22758,7 @@
         <v>67.90000000000001</v>
       </c>
       <c r="L149" t="n">
-        <v>29.1</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="150">
@@ -22794,7 +22794,7 @@
         <v>526</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>684</v>
+        <v>579</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>9.720000000000001</v>
@@ -22806,7 +22806,7 @@
         <v>68.3</v>
       </c>
       <c r="L150" t="n">
-        <v>29.4</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="151">
@@ -22842,7 +22842,7 @@
         <v>557</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>724</v>
+        <v>613</v>
       </c>
       <c r="I151" s="3" t="n">
         <v>10.37</v>
@@ -22854,7 +22854,7 @@
         <v>69.5</v>
       </c>
       <c r="L151" t="n">
-        <v>30.4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="152">
@@ -22890,7 +22890,7 @@
         <v>635</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>826</v>
+        <v>698</v>
       </c>
       <c r="I152" s="3" t="n">
         <v>11.88</v>
@@ -22902,7 +22902,7 @@
         <v>70.2</v>
       </c>
       <c r="L152" t="n">
-        <v>30.9</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="153">
@@ -22938,7 +22938,7 @@
         <v>627</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>815</v>
+        <v>690</v>
       </c>
       <c r="I153" s="3" t="n">
         <v>11.88</v>
@@ -22950,7 +22950,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="L153" t="n">
-        <v>32.6</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="154">
@@ -22986,7 +22986,7 @@
         <v>454</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>590</v>
+        <v>499</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>8.640000000000001</v>
@@ -22998,7 +22998,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="L154" t="n">
-        <v>33.2</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="155">
@@ -23034,7 +23034,7 @@
         <v>451</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>586</v>
+        <v>496</v>
       </c>
       <c r="I155" s="3" t="n">
         <v>8.640000000000001</v>
@@ -23046,7 +23046,7 @@
         <v>74.3</v>
       </c>
       <c r="L155" t="n">
-        <v>34.1</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="156">
@@ -23082,7 +23082,7 @@
         <v>451</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>586</v>
+        <v>496</v>
       </c>
       <c r="I156" s="3" t="n">
         <v>8.640000000000001</v>
@@ -23094,7 +23094,7 @@
         <v>74.3</v>
       </c>
       <c r="L156" t="n">
-        <v>34.1</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="157">
@@ -23130,7 +23130,7 @@
         <v>393</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>511</v>
+        <v>432</v>
       </c>
       <c r="I157" s="3" t="n">
         <v>7.56</v>
@@ -23142,7 +23142,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="L157" t="n">
-        <v>34.6</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="158">
@@ -23178,7 +23178,7 @@
         <v>391</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>508</v>
+        <v>430</v>
       </c>
       <c r="I158" s="3" t="n">
         <v>7.56</v>
@@ -23190,7 +23190,7 @@
         <v>76</v>
       </c>
       <c r="L158" t="n">
-        <v>35.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="159">
@@ -23226,7 +23226,7 @@
         <v>580</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>754</v>
+        <v>638</v>
       </c>
       <c r="I159" s="3" t="n">
         <v>11.23</v>
@@ -23238,7 +23238,7 @@
         <v>76.2</v>
       </c>
       <c r="L159" t="n">
-        <v>35.5</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="160">
@@ -23274,7 +23274,7 @@
         <v>496</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>645</v>
+        <v>546</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>9.720000000000001</v>
@@ -23286,7 +23286,7 @@
         <v>78.40000000000001</v>
       </c>
       <c r="L160" t="n">
-        <v>37.2</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="161">
@@ -23322,7 +23322,7 @@
         <v>627</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>815</v>
+        <v>690</v>
       </c>
       <c r="I161" s="3" t="n">
         <v>12.31</v>
@@ -23334,7 +23334,7 @@
         <v>78.59999999999999</v>
       </c>
       <c r="L161" t="n">
-        <v>37.4</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="162">
@@ -23370,7 +23370,7 @@
         <v>582</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>757</v>
+        <v>640</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>11.45</v>
@@ -23382,7 +23382,7 @@
         <v>79</v>
       </c>
       <c r="L162" t="n">
-        <v>37.6</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="163">
@@ -23418,7 +23418,7 @@
         <v>1467</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>1907</v>
+        <v>1614</v>
       </c>
       <c r="I163" s="3" t="n">
         <v>29.16</v>
@@ -23430,7 +23430,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="L163" t="n">
-        <v>39.2</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="164">
@@ -23466,7 +23466,7 @@
         <v>627</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>815</v>
+        <v>690</v>
       </c>
       <c r="I164" s="3" t="n">
         <v>12.53</v>
@@ -23478,7 +23478,7 @@
         <v>81.8</v>
       </c>
       <c r="L164" t="n">
-        <v>39.9</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="165">
@@ -23514,7 +23514,7 @@
         <v>604</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>785</v>
+        <v>664</v>
       </c>
       <c r="I165" s="3" t="n">
         <v>12.1</v>
@@ -23526,7 +23526,7 @@
         <v>82.3</v>
       </c>
       <c r="L165" t="n">
-        <v>40.3</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="166">
@@ -23562,7 +23562,7 @@
         <v>451</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>586</v>
+        <v>496</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>9.07</v>
@@ -23574,7 +23574,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="L166" t="n">
-        <v>40.8</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="167">
@@ -23610,7 +23610,7 @@
         <v>451</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>586</v>
+        <v>496</v>
       </c>
       <c r="I167" s="3" t="n">
         <v>9.07</v>
@@ -23622,7 +23622,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="L167" t="n">
-        <v>40.8</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="168">
@@ -23658,7 +23658,7 @@
         <v>416</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>541</v>
+        <v>458</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>8.43</v>
@@ -23670,7 +23670,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="L168" t="n">
-        <v>41.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="169">
@@ -23706,7 +23706,7 @@
         <v>416</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>541</v>
+        <v>458</v>
       </c>
       <c r="I169" s="3" t="n">
         <v>8.43</v>
@@ -23718,7 +23718,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="L169" t="n">
-        <v>41.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="170">
@@ -23754,7 +23754,7 @@
         <v>627</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>815</v>
+        <v>690</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>12.75</v>
@@ -23766,7 +23766,7 @@
         <v>85</v>
       </c>
       <c r="L170" t="n">
-        <v>42.3</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="171">
@@ -23802,7 +23802,7 @@
         <v>603</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>784</v>
+        <v>663</v>
       </c>
       <c r="I171" s="3" t="n">
         <v>12.31</v>
@@ -23814,7 +23814,7 @@
         <v>85.7</v>
       </c>
       <c r="L171" t="n">
-        <v>42.9</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="172">
@@ -23850,7 +23850,7 @@
         <v>423</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>550</v>
+        <v>465</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>8.640000000000001</v>
@@ -23862,7 +23862,7 @@
         <v>85.8</v>
       </c>
       <c r="L172" t="n">
-        <v>42.9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="173">
@@ -23898,7 +23898,7 @@
         <v>285</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="I173" s="3" t="n">
         <v>5.83</v>
@@ -23910,7 +23910,7 @@
         <v>86.3</v>
       </c>
       <c r="L173" t="n">
-        <v>43.5</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="174">
@@ -23946,7 +23946,7 @@
         <v>369</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>480</v>
+        <v>406</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>7.56</v>
@@ -23958,7 +23958,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="L174" t="n">
-        <v>43.3</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="175">
@@ -23994,7 +23994,7 @@
         <v>597</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>776</v>
+        <v>657</v>
       </c>
       <c r="I175" s="3" t="n">
         <v>12.53</v>
@@ -24006,7 +24006,7 @@
         <v>91</v>
       </c>
       <c r="L175" t="n">
-        <v>46.9</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="176">
@@ -24042,7 +24042,7 @@
         <v>358</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>465</v>
+        <v>394</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>7.56</v>
@@ -24054,7 +24054,7 @@
         <v>92.2</v>
       </c>
       <c r="L176" t="n">
-        <v>48</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -24090,7 +24090,7 @@
         <v>560</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>728</v>
+        <v>616</v>
       </c>
       <c r="I177" s="3" t="n">
         <v>11.88</v>
@@ -24102,7 +24102,7 @@
         <v>93</v>
       </c>
       <c r="L177" t="n">
-        <v>48.5</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="178">
@@ -24138,7 +24138,7 @@
         <v>500</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>10.8</v>
@@ -24150,7 +24150,7 @@
         <v>96.59999999999999</v>
       </c>
       <c r="L178" t="n">
-        <v>51.2</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="179">
@@ -24186,7 +24186,7 @@
         <v>347</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>451</v>
+        <v>382</v>
       </c>
       <c r="I179" s="3" t="n">
         <v>7.56</v>
@@ -24198,7 +24198,7 @@
         <v>98.3</v>
       </c>
       <c r="L179" t="n">
-        <v>52.5</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -24234,7 +24234,7 @@
         <v>1185</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>1540</v>
+        <v>1304</v>
       </c>
       <c r="I180" s="3" t="n">
         <v>25.92</v>
@@ -24246,7 +24246,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="L180" t="n">
-        <v>53.2</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="181">
@@ -24282,7 +24282,7 @@
         <v>434</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>564</v>
+        <v>477</v>
       </c>
       <c r="I181" s="3" t="n">
         <v>9.720000000000001</v>
@@ -24294,7 +24294,7 @@
         <v>103.9</v>
       </c>
       <c r="L181" t="n">
-        <v>56.9</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="182">
@@ -24330,7 +24330,7 @@
         <v>233</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="I182" s="3" t="n">
         <v>5.83</v>
@@ -24342,7 +24342,7 @@
         <v>127.9</v>
       </c>
       <c r="L182" t="n">
-        <v>75.2</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="183">
@@ -24378,7 +24378,7 @@
         <v>448</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>582</v>
+        <v>493</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>11.88</v>
@@ -24390,7 +24390,7 @@
         <v>141.3</v>
       </c>
       <c r="L183" t="n">
-        <v>85.7</v>
+        <v>119.3</v>
       </c>
     </row>
     <row r="184">
@@ -24426,7 +24426,7 @@
         <v>353</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>459</v>
+        <v>388</v>
       </c>
       <c r="I184" s="3" t="n">
         <v>9.720000000000001</v>
@@ -24438,7 +24438,7 @@
         <v>150.7</v>
       </c>
       <c r="L184" t="n">
-        <v>92.8</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="185">
@@ -24474,7 +24474,7 @@
         <v>131</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="I185" s="3" t="n">
         <v>3.67</v>
@@ -24486,7 +24486,7 @@
         <v>155</v>
       </c>
       <c r="L185" t="n">
-        <v>96.5</v>
+        <v>131.9</v>
       </c>
     </row>
     <row r="186">
@@ -24522,7 +24522,7 @@
         <v>94</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="I186" s="3" t="n">
         <v>2.81</v>
@@ -24534,7 +24534,7 @@
         <v>172.3</v>
       </c>
       <c r="L186" t="n">
-        <v>109.8</v>
+        <v>148.5</v>
       </c>
     </row>
     <row r="187">
@@ -24570,7 +24570,7 @@
         <v>104</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="I187" s="3" t="n">
         <v>3.24</v>
@@ -24582,7 +24582,7 @@
         <v>183.7</v>
       </c>
       <c r="L187" t="n">
-        <v>118.5</v>
+        <v>158.8</v>
       </c>
     </row>
     <row r="188">
@@ -24618,7 +24618,7 @@
         <v>82</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>2.59</v>
@@ -24630,7 +24630,7 @@
         <v>187.8</v>
       </c>
       <c r="L188" t="n">
-        <v>120.6</v>
+        <v>162.2</v>
       </c>
     </row>
     <row r="189">
@@ -24652,7 +24652,7 @@
         <v>674</v>
       </c>
       <c r="H189" s="5" t="n">
-        <v>876</v>
+        <v>741</v>
       </c>
       <c r="I189" s="6" t="inlineStr"/>
       <c r="J189" s="5" t="n">
@@ -24662,7 +24662,7 @@
         <v>41.6</v>
       </c>
       <c r="L189" s="4" t="n">
-        <v>8.9</v>
+        <v>28.8</v>
       </c>
     </row>
   </sheetData>
@@ -24762,7 +24762,7 @@
         <v>32.4</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="3">
@@ -24784,7 +24784,7 @@
         <v>12.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-13.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4">
@@ -24806,7 +24806,7 @@
         <v>47.6</v>
       </c>
       <c r="F4" t="n">
-        <v>13.6</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="5">
@@ -24828,7 +24828,7 @@
         <v>29.1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="6">
@@ -24850,7 +24850,7 @@
         <v>27.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="7">
@@ -24872,7 +24872,7 @@
         <v>49.3</v>
       </c>
       <c r="F7" t="n">
-        <v>14.8</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="8">
@@ -24894,7 +24894,7 @@
         <v>43.7</v>
       </c>
       <c r="F8" t="n">
-        <v>10.6</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="9">
@@ -24916,7 +24916,7 @@
         <v>47.2</v>
       </c>
       <c r="F9" t="n">
-        <v>13.3</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="10">
@@ -24938,7 +24938,7 @@
         <v>35.2</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -24960,7 +24960,7 @@
         <v>48.2</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="12">
@@ -24982,7 +24982,7 @@
         <v>55.8</v>
       </c>
       <c r="F12" t="n">
-        <v>19.8</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="13">
@@ -25004,7 +25004,7 @@
         <v>41.6</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8.9</v>
+        <v>28.8</v>
       </c>
     </row>
   </sheetData>
